--- a/tejas-backend/src/modules/kalman script/uploads/Recom_Scrap_Input_3 1.xlsx
+++ b/tejas-backend/src/modules/kalman script/uploads/Recom_Scrap_Input_3 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLW057\ScrapOptimisation\Uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ORMAE\JSW\ScrapOptimisation\ScrapOptimisation_Latest_With_GradeSpec_MatchingLogic\Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F263F3-B572-40A2-A3BA-1E32C56FE5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E158B0-CDE5-4DDB-B337-48DB987040EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="Target" sheetId="2" r:id="rId2"/>
     <sheet name="Parameters" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Input!$A$1:$AJ$48</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="147">
   <si>
     <t>Scrap Category</t>
   </si>
@@ -417,6 +420,63 @@
   </si>
   <si>
     <t>CHG-Scrap - Party Mix</t>
+  </si>
+  <si>
+    <t>Mo</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Maximum_Usage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventory </t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Yielded_Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Power_Cost ()</t>
+  </si>
+  <si>
+    <t>Flux+C ()</t>
+  </si>
+  <si>
+    <t>Total Yield + Power+ Flux Cost_old</t>
   </si>
 </sst>
 </file>
@@ -758,21 +818,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB48"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.90625" customWidth="1"/>
-    <col min="4" max="4" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.6328125" customWidth="1"/>
-    <col min="26" max="26" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="28.453125" customWidth="1"/>
-    <col min="28" max="28" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="22.90625" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" customWidth="1"/>
+    <col min="7" max="7" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="29" max="29" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.7265625" customWidth="1"/>
+    <col min="31" max="32" width="25.6328125" customWidth="1"/>
+    <col min="33" max="33" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="28.453125" customWidth="1"/>
+    <col min="36" max="37" width="26.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -783,82 +847,109 @@
         <v>87</v>
       </c>
       <c r="D1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="R1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="S1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="T1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="U1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="V1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="W1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="X1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="Y1" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AA1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AB1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AC1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AD1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AF1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AG1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AH1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AI1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AK1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -868,412 +959,535 @@
       <c r="C2" t="s">
         <v>88</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2">
         <v>0.22972499999999998</v>
       </c>
-      <c r="E2">
+      <c r="F2">
+        <v>459.45</v>
+      </c>
+      <c r="G2">
         <v>10000</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.5</v>
+      </c>
+      <c r="O2">
+        <v>1.5</v>
+      </c>
+      <c r="P2">
+        <v>0.5</v>
+      </c>
+      <c r="Q2">
+        <v>0.01</v>
+      </c>
+      <c r="R2">
+        <v>0.03</v>
+      </c>
+      <c r="S2">
+        <v>0.05</v>
+      </c>
+      <c r="T2">
+        <v>0.01</v>
+      </c>
+      <c r="U2">
+        <v>0.15</v>
+      </c>
+      <c r="V2">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="K2">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="L2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="M2">
-        <v>1E-4</v>
-      </c>
-      <c r="N2">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="O2">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="P2">
-        <v>1E-4</v>
-      </c>
-      <c r="Q2">
-        <v>1.5E-3</v>
-      </c>
-      <c r="R2">
-        <v>4.4999999999999999E-4</v>
-      </c>
-      <c r="T2">
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>95</v>
+      </c>
+      <c r="Y2">
+        <v>0.01</v>
+      </c>
+      <c r="Z2">
+        <v>250</v>
+      </c>
+      <c r="AA2">
+        <v>232</v>
+      </c>
+      <c r="AB2">
         <v>0.95</v>
       </c>
-      <c r="U2">
-        <v>250</v>
-      </c>
-      <c r="V2">
-        <v>232</v>
-      </c>
-      <c r="W2">
-        <v>0.95</v>
-      </c>
-      <c r="X2">
+      <c r="AC2">
         <v>0.24181578947368418</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
+        <v>483.63157894736838</v>
+      </c>
+      <c r="AE2">
         <v>5.8463999999999999E-3</v>
       </c>
-      <c r="Z2">
+      <c r="AF2">
+        <v>11.6928</v>
+      </c>
+      <c r="AG2">
         <v>1</v>
       </c>
-      <c r="AA2">
+      <c r="AH2">
         <v>1.3099999999999999E-2</v>
       </c>
-      <c r="AB2">
+      <c r="AI2">
+        <v>26.2</v>
+      </c>
+      <c r="AJ2">
         <v>0.26076218947368418</v>
       </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK2">
+        <v>521.5243789473684</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>36</v>
       </c>
       <c r="C3" t="s">
         <v>89</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3">
         <v>0.18590999999999999</v>
       </c>
-      <c r="E3">
+      <c r="F3">
+        <v>371.82</v>
+      </c>
+      <c r="G3">
         <v>1000</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
+        <v>1000</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>929.64615116695347</v>
+      </c>
+      <c r="L3">
         <v>9.2964615060159208E-3</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>3.456610317166839</v>
       </c>
-      <c r="J3">
-        <v>4.1399999999999999E-2</v>
-      </c>
-      <c r="K3">
-        <v>8.5000000000000006E-3</v>
-      </c>
-      <c r="L3">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="M3">
-        <v>2.0000000000000001E-4</v>
-      </c>
       <c r="N3">
-        <v>1.5E-3</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="O3">
-        <v>5.9999999999999995E-4</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q3">
-        <v>1.1000000000000001E-3</v>
+        <v>0.02</v>
       </c>
       <c r="R3">
-        <v>2.9999999999999997E-4</v>
+        <v>0.15</v>
       </c>
       <c r="S3">
-        <v>2.0000000000000001E-4</v>
+        <v>0.06</v>
       </c>
       <c r="T3">
-        <v>0.94</v>
+        <v>0</v>
       </c>
       <c r="U3">
+        <v>0.11</v>
+      </c>
+      <c r="V3">
+        <v>0.03</v>
+      </c>
+      <c r="W3">
+        <v>0.02</v>
+      </c>
+      <c r="X3">
+        <v>94</v>
+      </c>
+      <c r="Y3">
+        <v>0.02</v>
+      </c>
+      <c r="Z3">
         <v>250.18</v>
       </c>
-      <c r="V3">
+      <c r="AA3">
         <v>440</v>
       </c>
-      <c r="W3">
+      <c r="AB3">
         <v>0.8</v>
       </c>
-      <c r="X3">
+      <c r="AC3">
         <v>0.2323875</v>
       </c>
-      <c r="Y3">
+      <c r="AD3">
+        <v>464.77499999999998</v>
+      </c>
+      <c r="AE3">
         <v>1.1087999999999999E-2</v>
       </c>
-      <c r="Z3">
+      <c r="AF3">
+        <v>22.175999999999998</v>
+      </c>
+      <c r="AG3">
         <v>8</v>
       </c>
-      <c r="AA3">
+      <c r="AH3">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="AB3">
+      <c r="AI3">
+        <v>34.6</v>
+      </c>
+      <c r="AJ3">
         <v>0.26077549999999994</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK3">
+        <v>521.55099999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>37</v>
       </c>
       <c r="C4" t="s">
         <v>90</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4">
         <v>0.163575</v>
       </c>
-      <c r="E4">
+      <c r="F4">
+        <v>327.14999999999998</v>
+      </c>
+      <c r="G4">
         <v>1000</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
+        <v>1000</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1000</v>
+      </c>
+      <c r="L4">
         <v>9.9999999939185315E-3</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>3.271499998010448</v>
       </c>
-      <c r="J4">
-        <v>3.9E-2</v>
-      </c>
-      <c r="K4">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="L4">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="M4">
-        <v>2.9999999999999997E-4</v>
-      </c>
       <c r="N4">
-        <v>5.0000000000000001E-4</v>
+        <v>3.9</v>
       </c>
       <c r="O4">
-        <v>5.0000000000000001E-4</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="P4">
-        <v>2.0000000000000001E-4</v>
+        <v>0.36</v>
       </c>
       <c r="Q4">
-        <v>2.0000000000000001E-4</v>
+        <v>0.03</v>
       </c>
       <c r="R4">
-        <v>6.9999999999999999E-4</v>
+        <v>0.05</v>
       </c>
       <c r="S4">
-        <v>2.0000000000000001E-4</v>
+        <v>0.05</v>
       </c>
       <c r="T4">
-        <v>0.93</v>
+        <v>0.02</v>
       </c>
       <c r="U4">
+        <v>0.02</v>
+      </c>
+      <c r="V4">
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="W4">
+        <v>0.02</v>
+      </c>
+      <c r="X4">
+        <v>93</v>
+      </c>
+      <c r="Y4">
+        <v>0.02</v>
+      </c>
+      <c r="Z4">
         <v>250</v>
       </c>
-      <c r="V4">
+      <c r="AA4">
         <v>378</v>
       </c>
-      <c r="W4">
+      <c r="AB4">
         <v>0.8</v>
       </c>
-      <c r="X4">
+      <c r="AC4">
         <v>0.20446874999999995</v>
       </c>
-      <c r="Y4">
+      <c r="AD4">
+        <v>408.93749999999989</v>
+      </c>
+      <c r="AE4">
         <v>9.5256000000000004E-3</v>
       </c>
-      <c r="Z4">
+      <c r="AF4">
+        <v>19.051200000000001</v>
+      </c>
+      <c r="AG4">
         <v>9</v>
       </c>
-      <c r="AA4">
+      <c r="AH4">
         <v>1.7899999999999999E-2</v>
       </c>
-      <c r="AB4">
+      <c r="AI4">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="AJ4">
         <v>0.23189434999999994</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK4">
+        <v>463.78869999999989</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>38</v>
       </c>
       <c r="C5" t="s">
         <v>91</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
         <v>0.17955500000000002</v>
       </c>
-      <c r="E5">
+      <c r="F5">
+        <v>359.11</v>
+      </c>
+      <c r="G5">
         <v>10000</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
+        <v>10000</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>10000</v>
+      </c>
+      <c r="L5">
         <v>9.9999999939185333E-2</v>
       </c>
-      <c r="I5">
+      <c r="M5">
         <v>35.910999978160852</v>
       </c>
-      <c r="J5">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="K5">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="L5">
-        <v>7.6499999999999999E-2</v>
-      </c>
-      <c r="M5">
-        <v>4.8000000000000001E-4</v>
-      </c>
       <c r="N5">
-        <v>5.5999999999999995E-4</v>
+        <v>3.6999999999999997</v>
       </c>
       <c r="O5">
-        <v>3.4000000000000002E-4</v>
+        <v>1.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>7.6499999999999995</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>5.5999999999999994E-2</v>
       </c>
       <c r="S5">
-        <v>2.0000000000000001E-4</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="T5">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.02</v>
+      </c>
+      <c r="X5">
+        <v>95</v>
+      </c>
+      <c r="Y5">
+        <v>0.02</v>
+      </c>
+      <c r="Z5">
         <v>250</v>
       </c>
-      <c r="V5">
+      <c r="AA5">
         <v>250</v>
       </c>
-      <c r="W5">
+      <c r="AB5">
         <v>0.93</v>
       </c>
-      <c r="X5">
+      <c r="AC5">
         <v>0.19306989247311823</v>
       </c>
-      <c r="Y5">
+      <c r="AD5">
+        <v>386.13978494623649</v>
+      </c>
+      <c r="AE5">
         <v>6.3E-3</v>
       </c>
-      <c r="Z5">
+      <c r="AF5">
+        <v>12.6</v>
+      </c>
+      <c r="AG5">
         <v>3</v>
       </c>
-      <c r="AA5">
+      <c r="AH5">
         <v>1.43E-2</v>
       </c>
-      <c r="AB5">
+      <c r="AI5">
+        <v>28.6</v>
+      </c>
+      <c r="AJ5">
         <v>0.21366989247311829</v>
       </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK5">
+        <v>427.33978494623659</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>92</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
         <v>0.162605</v>
       </c>
-      <c r="E6">
+      <c r="F6">
+        <v>325.20999999999998</v>
+      </c>
+      <c r="G6">
         <v>1000</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="L6">
         <v>9.9999999939185315E-3</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>3.252099998022246</v>
       </c>
-      <c r="J6">
-        <v>2.86E-2</v>
-      </c>
-      <c r="K6">
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="L6">
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="M6">
-        <v>1E-4</v>
-      </c>
       <c r="N6">
-        <v>2.9999999999999997E-4</v>
+        <v>2.86</v>
       </c>
       <c r="O6">
-        <v>7.0000000000000001E-3</v>
+        <v>0.67</v>
       </c>
       <c r="P6">
-        <v>1E-4</v>
+        <v>0.67</v>
       </c>
       <c r="Q6">
-        <v>1E-4</v>
+        <v>0.01</v>
       </c>
       <c r="R6">
-        <v>2.5000000000000001E-4</v>
+        <v>0.03</v>
       </c>
       <c r="S6">
-        <v>1E-4</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="T6">
-        <v>0.90290000000000004</v>
+        <v>0.01</v>
       </c>
       <c r="U6">
+        <v>0.01</v>
+      </c>
+      <c r="V6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="W6">
+        <v>0.01</v>
+      </c>
+      <c r="X6">
+        <v>90.29</v>
+      </c>
+      <c r="Y6">
+        <v>0.01</v>
+      </c>
+      <c r="Z6">
         <v>300</v>
       </c>
-      <c r="V6">
+      <c r="AA6">
         <v>607</v>
       </c>
-      <c r="W6">
+      <c r="AB6">
         <v>0.8</v>
       </c>
-      <c r="X6">
+      <c r="AC6">
         <v>0.20325624999999994</v>
       </c>
-      <c r="Y6">
+      <c r="AD6">
+        <v>406.51249999999987</v>
+      </c>
+      <c r="AE6">
         <v>1.52964E-2</v>
       </c>
-      <c r="Z6">
+      <c r="AF6">
+        <v>30.5928</v>
+      </c>
+      <c r="AG6">
         <v>8</v>
       </c>
-      <c r="AA6">
+      <c r="AH6">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="AB6">
+      <c r="AI6">
+        <v>34.6</v>
+      </c>
+      <c r="AJ6">
         <v>0.23585265000000002</v>
       </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK6">
+        <v>471.70530000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1283,166 +1497,208 @@
       <c r="C7" t="s">
         <v>93</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.17861000000000002</v>
       </c>
-      <c r="E7">
+      <c r="F7">
+        <v>357.22</v>
+      </c>
+      <c r="G7">
         <v>1000</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7">
+        <v>0.43</v>
+      </c>
+      <c r="P7">
+        <v>0.62</v>
+      </c>
+      <c r="Q7">
         <v>0.03</v>
       </c>
-      <c r="K7">
-        <v>4.3E-3</v>
-      </c>
-      <c r="L7">
-        <v>6.1999999999999998E-3</v>
-      </c>
-      <c r="M7">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="N7">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="O7">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="P7">
-        <v>1E-4</v>
-      </c>
-      <c r="Q7">
-        <v>6.0000000000000002E-5</v>
-      </c>
       <c r="R7">
-        <v>4.6999999999999999E-4</v>
+        <v>0.03</v>
       </c>
       <c r="S7">
-        <v>1E-4</v>
+        <v>0.03</v>
       </c>
       <c r="T7">
-        <v>0.9</v>
+        <v>0.01</v>
       </c>
       <c r="U7">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="V7">
+        <v>4.7E-2</v>
+      </c>
+      <c r="W7">
+        <v>0.01</v>
+      </c>
+      <c r="X7">
+        <v>90</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
         <v>300</v>
       </c>
-      <c r="V7">
+      <c r="AA7">
         <v>607</v>
       </c>
-      <c r="W7">
+      <c r="AB7">
         <v>0.75</v>
       </c>
-      <c r="X7">
+      <c r="AC7">
         <v>0.2381466666666667</v>
       </c>
-      <c r="Y7">
+      <c r="AD7">
+        <v>476.29333333333341</v>
+      </c>
+      <c r="AE7">
         <v>1.52964E-2</v>
       </c>
-      <c r="Z7">
+      <c r="AF7">
+        <v>30.5928</v>
+      </c>
+      <c r="AG7">
         <v>8</v>
       </c>
-      <c r="AA7">
+      <c r="AH7">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="AB7">
+      <c r="AI7">
+        <v>34.6</v>
+      </c>
+      <c r="AJ7">
         <v>0.27074306666666664</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK7">
+        <v>541.48613333333333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>94</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.19046000000000002</v>
       </c>
-      <c r="E8">
+      <c r="F8">
+        <v>380.92</v>
+      </c>
+      <c r="G8">
         <v>1000</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
       <c r="H8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
+      <c r="L8">
         <v>9.9999999939185315E-3</v>
       </c>
-      <c r="I8">
+      <c r="M8">
         <v>3.809199997683447</v>
       </c>
-      <c r="J8">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>2.0000000000000001E-4</v>
-      </c>
       <c r="N8">
-        <v>1E-3</v>
+        <v>1.5</v>
       </c>
       <c r="O8">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>8.0000000000000004E-4</v>
+        <v>0.02</v>
       </c>
       <c r="R8">
-        <v>2.9999999999999997E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S8">
-        <v>2.9999999999999997E-4</v>
+        <v>0.1</v>
       </c>
       <c r="T8">
-        <v>0.9</v>
+        <v>0.01</v>
       </c>
       <c r="U8">
+        <v>0.08</v>
+      </c>
+      <c r="V8">
+        <v>0.03</v>
+      </c>
+      <c r="W8">
+        <v>0.03</v>
+      </c>
+      <c r="X8">
+        <v>90</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
         <v>311.95</v>
       </c>
-      <c r="V8">
+      <c r="AA8">
         <v>607</v>
       </c>
-      <c r="W8">
+      <c r="AB8">
         <v>0.86</v>
       </c>
-      <c r="X8">
+      <c r="AC8">
         <v>0.22146511627906981</v>
       </c>
-      <c r="Y8">
+      <c r="AD8">
+        <v>442.93023255813961</v>
+      </c>
+      <c r="AE8">
         <v>1.52964E-2</v>
       </c>
-      <c r="Z8">
+      <c r="AF8">
+        <v>30.5928</v>
+      </c>
+      <c r="AG8">
         <v>8</v>
       </c>
-      <c r="AA8">
+      <c r="AH8">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="AB8">
+      <c r="AI8">
+        <v>34.6</v>
+      </c>
+      <c r="AJ8">
         <v>0.25406151627906981</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK8">
+        <v>508.12303255813964</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1452,355 +1708,442 @@
       <c r="C9" t="s">
         <v>95</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9">
         <v>0.18235499999999999</v>
       </c>
-      <c r="E9">
+      <c r="F9">
+        <v>364.71</v>
+      </c>
+      <c r="G9">
         <v>50000</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
       <c r="H9">
+        <v>50000</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>36739.583958180709</v>
+      </c>
+      <c r="L9">
         <v>0.3673958393583765</v>
       </c>
-      <c r="I9">
+      <c r="M9">
         <v>133.99293657239349</v>
       </c>
-      <c r="J9">
-        <v>1E-3</v>
-      </c>
-      <c r="K9">
-        <v>1E-3</v>
-      </c>
-      <c r="L9">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="M9">
-        <v>1E-3</v>
-      </c>
       <c r="N9">
-        <v>1E-3</v>
+        <v>0.1</v>
       </c>
       <c r="O9">
-        <v>8.0000000000000004E-4</v>
+        <v>0.1</v>
       </c>
       <c r="P9">
-        <v>1E-4</v>
+        <v>0.5</v>
       </c>
       <c r="Q9">
-        <v>4.0000000000000002E-4</v>
+        <v>0.1</v>
       </c>
       <c r="R9">
-        <v>5.0000000000000001E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S9">
-        <v>2.9999999999999997E-4</v>
+        <v>0.08</v>
       </c>
       <c r="T9">
-        <v>0.98</v>
+        <v>0.01</v>
       </c>
       <c r="U9">
+        <v>0.04</v>
+      </c>
+      <c r="V9">
+        <v>0.05</v>
+      </c>
+      <c r="W9">
+        <v>0.03</v>
+      </c>
+      <c r="X9">
+        <v>98</v>
+      </c>
+      <c r="Y9">
+        <v>0.03</v>
+      </c>
+      <c r="Z9">
         <v>65</v>
       </c>
-      <c r="V9">
+      <c r="AA9">
         <v>322</v>
       </c>
-      <c r="W9">
+      <c r="AB9">
         <v>0.94</v>
       </c>
-      <c r="X9">
+      <c r="AC9">
         <v>0.19399468085106386</v>
       </c>
-      <c r="Y9">
+      <c r="AD9">
+        <v>387.98936170212772</v>
+      </c>
+      <c r="AE9">
         <v>8.114399999999999E-3</v>
       </c>
-      <c r="Z9">
+      <c r="AF9">
+        <v>16.2288</v>
+      </c>
+      <c r="AG9">
         <v>3</v>
       </c>
-      <c r="AA9">
+      <c r="AH9">
         <v>1.43E-2</v>
       </c>
-      <c r="AB9">
+      <c r="AI9">
+        <v>28.6</v>
+      </c>
+      <c r="AJ9">
         <v>0.21640908085106386</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK9">
+        <v>432.81816170212772</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>96</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10">
         <v>0.17845</v>
       </c>
-      <c r="E10">
+      <c r="F10">
+        <v>356.9</v>
+      </c>
+      <c r="G10">
         <v>5000</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
       <c r="H10">
+        <v>5000</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>5000</v>
+      </c>
+      <c r="L10">
         <v>4.9999999969592659E-2</v>
       </c>
-      <c r="I10">
+      <c r="M10">
         <v>17.84499998914762</v>
       </c>
-      <c r="J10">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="K10">
-        <v>1E-3</v>
-      </c>
-      <c r="L10">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="M10">
-        <v>1E-3</v>
-      </c>
       <c r="N10">
-        <v>5.0000000000000001E-4</v>
+        <v>0.06</v>
       </c>
       <c r="O10">
-        <v>5.0000000000000001E-4</v>
+        <v>0.1</v>
       </c>
       <c r="P10">
-        <v>3.0000000000000001E-5</v>
+        <v>0.32</v>
       </c>
       <c r="Q10">
-        <v>2.0000000000000001E-4</v>
+        <v>0.1</v>
       </c>
       <c r="R10">
-        <v>1E-4</v>
+        <v>0.05</v>
       </c>
       <c r="S10">
-        <v>1.4999999999999999E-4</v>
+        <v>0.05</v>
       </c>
       <c r="T10">
-        <v>0.98</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U10">
+        <v>0.02</v>
+      </c>
+      <c r="V10">
+        <v>0.01</v>
+      </c>
+      <c r="W10">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="X10">
+        <v>98</v>
+      </c>
+      <c r="Y10">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Z10">
         <v>99.823999999999998</v>
       </c>
-      <c r="V10">
+      <c r="AA10">
         <v>304</v>
       </c>
-      <c r="W10">
+      <c r="AB10">
         <v>0.88</v>
       </c>
-      <c r="X10">
+      <c r="AC10">
         <v>0.20278409090909091</v>
       </c>
-      <c r="Y10">
+      <c r="AD10">
+        <v>405.56818181818181</v>
+      </c>
+      <c r="AE10">
         <v>7.6607999999999997E-3</v>
       </c>
-      <c r="Z10">
+      <c r="AF10">
+        <v>15.3216</v>
+      </c>
+      <c r="AG10">
         <v>5</v>
       </c>
-      <c r="AA10">
+      <c r="AH10">
         <v>1.55E-2</v>
       </c>
-      <c r="AB10">
+      <c r="AI10">
+        <v>31</v>
+      </c>
+      <c r="AJ10">
         <v>0.2259448909090909</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK10">
+        <v>451.8897818181818</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>97</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.27600000000000002</v>
       </c>
-      <c r="E11">
+      <c r="F11">
+        <v>552</v>
+      </c>
+      <c r="G11">
         <v>1000</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
       <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J11">
-        <v>5.9999999999999995E-4</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>2.9999999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>3.2000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>8.0000000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>6.9999999999999999E-4</v>
+        <v>0.06</v>
       </c>
       <c r="O11">
-        <v>8.0000000000000004E-4</v>
+        <v>0.03</v>
       </c>
       <c r="P11">
-        <v>3.2000000000000002E-3</v>
+        <v>0.32</v>
       </c>
       <c r="Q11">
-        <v>8.0000000000000004E-4</v>
+        <v>0.08</v>
       </c>
       <c r="R11">
-        <v>1E-3</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="S11">
-        <v>2.0000000000000001E-4</v>
+        <v>0.08</v>
       </c>
       <c r="T11">
-        <v>0.98</v>
+        <v>0.32</v>
       </c>
       <c r="U11">
+        <v>0.08</v>
+      </c>
+      <c r="V11">
+        <v>0.1</v>
+      </c>
+      <c r="W11">
+        <v>0.02</v>
+      </c>
+      <c r="X11">
+        <v>98</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
         <v>49.91</v>
       </c>
-      <c r="V11">
+      <c r="AA11">
         <v>345</v>
       </c>
-      <c r="W11">
+      <c r="AB11">
         <v>0.94</v>
       </c>
-      <c r="X11">
+      <c r="AC11">
         <v>0.29361702127659578</v>
       </c>
-      <c r="Y11">
+      <c r="AD11">
+        <v>587.23404255319156</v>
+      </c>
+      <c r="AE11">
         <v>8.6940000000000003E-3</v>
       </c>
-      <c r="Z11">
+      <c r="AF11">
+        <v>17.388000000000002</v>
+      </c>
+      <c r="AG11">
         <v>3</v>
       </c>
-      <c r="AA11">
+      <c r="AH11">
         <v>1.43E-2</v>
       </c>
-      <c r="AB11">
+      <c r="AI11">
+        <v>28.6</v>
+      </c>
+      <c r="AJ11">
         <v>0.31661102127659579</v>
       </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK11">
+        <v>633.22204255319161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>98</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12">
         <v>0.17845</v>
       </c>
-      <c r="E12">
+      <c r="F12">
+        <v>356.9</v>
+      </c>
+      <c r="G12">
         <v>1000</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
       <c r="H12">
+        <v>1000</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>999.99999907939196</v>
+      </c>
+      <c r="L12">
         <v>9.9999999847124512E-3</v>
       </c>
-      <c r="I12">
+      <c r="M12">
         <v>3.5689999945438742</v>
       </c>
-      <c r="J12">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="K12">
-        <v>1E-3</v>
-      </c>
-      <c r="L12">
+      <c r="N12">
+        <v>0.06</v>
+      </c>
+      <c r="O12">
+        <v>0.1</v>
+      </c>
+      <c r="P12">
+        <v>1.5</v>
+      </c>
+      <c r="Q12">
+        <v>0.1</v>
+      </c>
+      <c r="R12">
+        <v>0.1</v>
+      </c>
+      <c r="S12">
+        <v>0.1</v>
+      </c>
+      <c r="T12">
+        <v>0.01</v>
+      </c>
+      <c r="U12">
+        <v>0.03</v>
+      </c>
+      <c r="V12">
+        <v>0.05</v>
+      </c>
+      <c r="W12">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="M12">
-        <v>1E-3</v>
-      </c>
-      <c r="N12">
-        <v>1E-3</v>
-      </c>
-      <c r="O12">
-        <v>1E-3</v>
-      </c>
-      <c r="P12">
-        <v>1E-4</v>
-      </c>
-      <c r="Q12">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="R12">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="S12">
-        <v>1.4999999999999999E-4</v>
-      </c>
-      <c r="T12">
-        <v>0.98</v>
-      </c>
-      <c r="U12">
+      <c r="X12">
+        <v>98</v>
+      </c>
+      <c r="Y12">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Z12">
         <v>89.84</v>
       </c>
-      <c r="V12">
+      <c r="AA12">
         <v>365</v>
       </c>
-      <c r="W12">
+      <c r="AB12">
         <v>0.86</v>
       </c>
-      <c r="X12">
+      <c r="AC12">
         <v>0.20749999999999999</v>
       </c>
-      <c r="Y12">
+      <c r="AD12">
+        <v>415</v>
+      </c>
+      <c r="AE12">
         <v>9.1979999999999996E-3</v>
       </c>
-      <c r="Z12">
+      <c r="AF12">
+        <v>18.396000000000001</v>
+      </c>
+      <c r="AG12">
         <v>5</v>
       </c>
-      <c r="AA12">
+      <c r="AH12">
         <v>1.55E-2</v>
       </c>
-      <c r="AB12">
+      <c r="AI12">
+        <v>31</v>
+      </c>
+      <c r="AJ12">
         <v>0.23219800000000002</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK12">
+        <v>464.39600000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>99</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.25892999999999999</v>
       </c>
-      <c r="E13">
+      <c r="F13">
+        <v>517.86</v>
+      </c>
+      <c r="G13">
         <v>1000</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
       <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1833,48 +2176,75 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>98</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
         <v>39.92</v>
       </c>
-      <c r="V13">
+      <c r="AA13">
         <v>345</v>
       </c>
-      <c r="W13">
+      <c r="AB13">
         <v>0.88</v>
       </c>
-      <c r="X13">
+      <c r="AC13">
         <v>0.2942386363636364</v>
       </c>
-      <c r="Y13">
+      <c r="AD13">
+        <v>588.47727272727275</v>
+      </c>
+      <c r="AE13">
         <v>8.6940000000000003E-3</v>
       </c>
-      <c r="Z13">
+      <c r="AF13">
+        <v>17.388000000000002</v>
+      </c>
+      <c r="AG13">
         <v>5</v>
       </c>
-      <c r="AA13">
+      <c r="AH13">
         <v>1.55E-2</v>
       </c>
-      <c r="AB13">
+      <c r="AI13">
+        <v>31</v>
+      </c>
+      <c r="AJ13">
         <v>0.31843263636363639</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK13">
+        <v>636.86527272727278</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>46</v>
       </c>
       <c r="C14" t="s">
         <v>100</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14">
         <v>0.179315</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
       <c r="F14">
-        <v>0</v>
+        <v>358.63</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1882,82 +2252,103 @@
       <c r="H14">
         <v>0</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
       <c r="J14">
-        <v>8.0000000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>5.9999999999999995E-4</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>5.9999999999999995E-4</v>
+        <v>0.08</v>
       </c>
       <c r="O14">
-        <v>5.9999999999999995E-4</v>
+        <v>0.05</v>
       </c>
       <c r="P14">
-        <v>2.9999999999999997E-4</v>
+        <v>0.5</v>
       </c>
       <c r="Q14">
-        <v>2.0000000000000001E-4</v>
+        <v>0.06</v>
       </c>
       <c r="R14">
-        <v>2.9999999999999997E-4</v>
+        <v>0.06</v>
       </c>
       <c r="S14">
-        <v>2.0000000000000001E-4</v>
+        <v>0.06</v>
       </c>
       <c r="T14">
-        <v>0.98</v>
+        <v>0.03</v>
       </c>
       <c r="U14">
+        <v>0.02</v>
+      </c>
+      <c r="V14">
+        <v>0.03</v>
+      </c>
+      <c r="W14">
+        <v>0.02</v>
+      </c>
+      <c r="X14">
+        <v>98</v>
+      </c>
+      <c r="Y14">
+        <v>0.02</v>
+      </c>
+      <c r="Z14">
         <v>74.86</v>
       </c>
-      <c r="V14">
+      <c r="AA14">
         <v>365</v>
       </c>
-      <c r="W14">
+      <c r="AB14">
         <v>0.9</v>
       </c>
-      <c r="X14">
+      <c r="AC14">
         <v>0.19923888888888891</v>
       </c>
-      <c r="Y14">
+      <c r="AD14">
+        <v>398.47777777777782</v>
+      </c>
+      <c r="AE14">
         <v>9.1979999999999996E-3</v>
       </c>
-      <c r="Z14">
+      <c r="AF14">
+        <v>18.396000000000001</v>
+      </c>
+      <c r="AG14">
         <v>4</v>
       </c>
-      <c r="AA14">
+      <c r="AH14">
         <v>1.49E-2</v>
       </c>
-      <c r="AB14">
+      <c r="AI14">
+        <v>29.8</v>
+      </c>
+      <c r="AJ14">
         <v>0.22333688888888889</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK14">
+        <v>446.67377777777779</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>47</v>
       </c>
       <c r="C15" t="s">
         <v>101</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.16741</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
       <c r="F15">
-        <v>0</v>
+        <v>334.82</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1965,82 +2356,103 @@
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
       <c r="J15">
-        <v>8.0000000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>2.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>1E-3</v>
+        <v>0.08</v>
       </c>
       <c r="O15">
-        <v>1E-3</v>
+        <v>0.25</v>
       </c>
       <c r="P15">
-        <v>3.0000000000000001E-3</v>
+        <v>0.4</v>
       </c>
       <c r="Q15">
-        <v>2.9999999999999997E-4</v>
+        <v>0.1</v>
       </c>
       <c r="R15">
-        <v>5.0000000000000001E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S15">
-        <v>2.0000000000000001E-4</v>
+        <v>0.1</v>
       </c>
       <c r="T15">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="U15">
+        <v>0.03</v>
+      </c>
+      <c r="V15">
+        <v>0.05</v>
+      </c>
+      <c r="W15">
+        <v>0.02</v>
+      </c>
+      <c r="X15">
+        <v>90</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
         <v>74.849999999999994</v>
       </c>
-      <c r="V15">
+      <c r="AA15">
         <v>365</v>
       </c>
-      <c r="W15">
+      <c r="AB15">
         <v>0.88</v>
       </c>
-      <c r="X15">
+      <c r="AC15">
         <v>0.19023863636363633</v>
       </c>
-      <c r="Y15">
+      <c r="AD15">
+        <v>380.47727272727269</v>
+      </c>
+      <c r="AE15">
         <v>9.1979999999999996E-3</v>
       </c>
-      <c r="Z15">
+      <c r="AF15">
+        <v>18.396000000000001</v>
+      </c>
+      <c r="AG15">
         <v>7</v>
       </c>
-      <c r="AA15">
+      <c r="AH15">
         <v>1.67E-2</v>
       </c>
-      <c r="AB15">
+      <c r="AI15">
+        <v>33.4</v>
+      </c>
+      <c r="AJ15">
         <v>0.21613663636363634</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK15">
+        <v>432.27327272727268</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>48</v>
       </c>
       <c r="C16" t="s">
         <v>102</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.15010499999999999</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
       <c r="F16">
-        <v>0</v>
+        <v>300.20999999999998</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2048,82 +2460,103 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
       <c r="J16">
-        <v>8.0000000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>2.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>5.9999999999999995E-4</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>5.9999999999999995E-4</v>
+        <v>0.08</v>
       </c>
       <c r="O16">
-        <v>5.9999999999999995E-4</v>
+        <v>0.25</v>
       </c>
       <c r="P16">
-        <v>2.9999999999999997E-4</v>
+        <v>0.4</v>
       </c>
       <c r="Q16">
-        <v>2.0000000000000001E-4</v>
+        <v>0.06</v>
       </c>
       <c r="R16">
-        <v>2.9999999999999997E-4</v>
+        <v>0.06</v>
       </c>
       <c r="S16">
-        <v>2.0000000000000001E-4</v>
+        <v>0.06</v>
       </c>
       <c r="T16">
-        <v>0.97</v>
+        <v>0.03</v>
       </c>
       <c r="U16">
+        <v>0.02</v>
+      </c>
+      <c r="V16">
+        <v>0.03</v>
+      </c>
+      <c r="W16">
+        <v>0.02</v>
+      </c>
+      <c r="X16">
+        <v>97</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
         <v>64.8</v>
       </c>
-      <c r="V16">
+      <c r="AA16">
         <v>350</v>
       </c>
-      <c r="W16">
+      <c r="AB16">
         <v>0.93</v>
       </c>
-      <c r="X16">
+      <c r="AC16">
         <v>0.16140322580645158</v>
       </c>
-      <c r="Y16">
+      <c r="AD16">
+        <v>322.80645161290317</v>
+      </c>
+      <c r="AE16">
         <v>8.8199999999999997E-3</v>
       </c>
-      <c r="Z16">
+      <c r="AF16">
+        <v>17.64</v>
+      </c>
+      <c r="AG16">
         <v>3</v>
       </c>
-      <c r="AA16">
+      <c r="AH16">
         <v>1.43E-2</v>
       </c>
-      <c r="AB16">
+      <c r="AI16">
+        <v>28.6</v>
+      </c>
+      <c r="AJ16">
         <v>0.18452322580645159</v>
       </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK16">
+        <v>369.04645161290318</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>49</v>
       </c>
       <c r="C17" t="s">
         <v>103</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.14657000000000001</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
       <c r="F17">
-        <v>0</v>
+        <v>293.14</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2131,82 +2564,106 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
       <c r="J17">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>1.15E-3</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>1E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O17">
-        <v>1E-3</v>
+        <v>0.1</v>
       </c>
       <c r="P17">
-        <v>1E-3</v>
+        <v>0.5</v>
       </c>
       <c r="Q17">
-        <v>2.9999999999999997E-4</v>
+        <v>0.11499999999999999</v>
       </c>
       <c r="R17">
-        <v>5.0000000000000001E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S17">
-        <v>2.0000000000000001E-4</v>
+        <v>0.1</v>
       </c>
       <c r="T17">
-        <v>0.97</v>
+        <v>0.1</v>
       </c>
       <c r="U17">
+        <v>0.03</v>
+      </c>
+      <c r="V17">
+        <v>0.05</v>
+      </c>
+      <c r="W17">
+        <v>0.02</v>
+      </c>
+      <c r="X17">
+        <v>97</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
         <v>69.87</v>
       </c>
-      <c r="V17">
+      <c r="AA17">
         <v>345</v>
       </c>
-      <c r="W17">
+      <c r="AB17">
         <v>0.88</v>
       </c>
-      <c r="X17">
+      <c r="AC17">
         <v>0.16655681818181819</v>
       </c>
-      <c r="Y17">
+      <c r="AD17">
+        <v>333.11363636363637</v>
+      </c>
+      <c r="AE17">
         <v>8.6940000000000003E-3</v>
       </c>
-      <c r="Z17">
+      <c r="AF17">
+        <v>17.388000000000002</v>
+      </c>
+      <c r="AG17">
         <v>6</v>
       </c>
-      <c r="AA17">
+      <c r="AH17">
         <v>1.61E-2</v>
       </c>
-      <c r="AB17">
+      <c r="AI17">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="AJ17">
         <v>0.19135081818181815</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK17">
+        <v>382.70163636363628</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>50</v>
       </c>
       <c r="C18" t="s">
         <v>104</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18">
         <v>0.13972701883692901</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
       <c r="F18">
-        <v>0</v>
+        <v>279.45403767385801</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2214,82 +2671,103 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
       <c r="J18">
-        <v>5.9999999999999995E-4</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>1.35E-2</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>5.0000000000000001E-4</v>
+        <v>0.06</v>
       </c>
       <c r="O18">
-        <v>4.0000000000000002E-4</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="P18">
-        <v>1E-4</v>
+        <v>1.35</v>
       </c>
       <c r="Q18">
-        <v>1E-4</v>
+        <v>0.05</v>
       </c>
       <c r="R18">
-        <v>1E-4</v>
+        <v>0.05</v>
       </c>
       <c r="S18">
-        <v>1E-4</v>
+        <v>0.04</v>
       </c>
       <c r="T18">
-        <v>0.97</v>
+        <v>0.01</v>
       </c>
       <c r="U18">
+        <v>0.01</v>
+      </c>
+      <c r="V18">
+        <v>0.01</v>
+      </c>
+      <c r="W18">
+        <v>0.01</v>
+      </c>
+      <c r="X18">
+        <v>97</v>
+      </c>
+      <c r="Y18">
+        <v>0.01</v>
+      </c>
+      <c r="Z18">
         <v>200</v>
       </c>
-      <c r="V18">
+      <c r="AA18">
         <v>318</v>
       </c>
-      <c r="W18">
+      <c r="AB18">
         <v>0.95</v>
       </c>
-      <c r="X18">
+      <c r="AC18">
         <v>0.1470810724599253</v>
       </c>
-      <c r="Y18">
+      <c r="AD18">
+        <v>294.16214491985062</v>
+      </c>
+      <c r="AE18">
         <v>8.0136000000000009E-3</v>
       </c>
-      <c r="Z18">
+      <c r="AF18">
+        <v>16.027200000000001</v>
+      </c>
+      <c r="AG18">
         <v>2</v>
       </c>
-      <c r="AA18">
+      <c r="AH18">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="AB18">
+      <c r="AI18">
+        <v>27.4</v>
+      </c>
+      <c r="AJ18">
         <v>0.16879467245992524</v>
       </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK18">
+        <v>337.58934491985048</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>51</v>
       </c>
       <c r="C19" t="s">
         <v>105</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.17861000000000002</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
       <c r="F19">
-        <v>0</v>
+        <v>357.22</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2297,68 +2775,92 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
       <c r="J19">
-        <v>6.0999999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>3.46E-3</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>1.35E-2</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>4.0999999999999999E-4</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>5.1999999999999995E-4</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="O19">
-        <v>3.3E-4</v>
+        <v>0.34599999999999997</v>
       </c>
       <c r="P19">
-        <v>1E-4</v>
+        <v>1.35</v>
       </c>
       <c r="Q19">
-        <v>1E-4</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="R19">
-        <v>1E-4</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="S19">
-        <v>1E-4</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="T19">
-        <v>0.97</v>
+        <v>0.01</v>
       </c>
       <c r="U19">
+        <v>0.01</v>
+      </c>
+      <c r="V19">
+        <v>0.01</v>
+      </c>
+      <c r="W19">
+        <v>0.01</v>
+      </c>
+      <c r="X19">
+        <v>97</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
         <v>129</v>
       </c>
-      <c r="V19">
+      <c r="AA19">
         <v>318</v>
       </c>
-      <c r="W19">
+      <c r="AB19">
         <v>0.94</v>
       </c>
-      <c r="X19">
+      <c r="AC19">
         <v>0.19001063829787238</v>
       </c>
-      <c r="Y19">
+      <c r="AD19">
+        <v>380.02127659574472</v>
+      </c>
+      <c r="AE19">
         <v>8.0136000000000009E-3</v>
       </c>
-      <c r="Z19">
+      <c r="AF19">
+        <v>16.027200000000001</v>
+      </c>
+      <c r="AG19">
         <v>3</v>
       </c>
-      <c r="AA19">
+      <c r="AH19">
         <v>1.43E-2</v>
       </c>
-      <c r="AB19">
+      <c r="AI19">
+        <v>28.6</v>
+      </c>
+      <c r="AJ19">
         <v>0.21232423829787234</v>
       </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK19">
+        <v>424.64847659574468</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -2368,415 +2870,523 @@
       <c r="C20" t="s">
         <v>106</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20">
         <v>0.16258500000000001</v>
       </c>
-      <c r="E20">
+      <c r="F20">
+        <v>325.17</v>
+      </c>
+      <c r="G20">
         <v>50000</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
       <c r="H20">
+        <v>50000</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>28454.60358025684</v>
+      </c>
+      <c r="L20">
         <v>0.28454603562952258</v>
       </c>
-      <c r="I20">
+      <c r="M20">
         <v>92.525834405651878</v>
       </c>
-      <c r="J20">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="K20">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="L20">
-        <v>8.7899999999999992E-3</v>
-      </c>
-      <c r="M20">
-        <v>1.6900000000000001E-3</v>
-      </c>
       <c r="N20">
-        <v>1.1199999999999999E-3</v>
+        <v>0.25</v>
       </c>
       <c r="O20">
-        <v>1.08E-3</v>
+        <v>0.25</v>
       </c>
       <c r="P20">
-        <v>2.0000000000000001E-4</v>
+        <v>0.87899999999999989</v>
       </c>
       <c r="Q20">
-        <v>4.0000000000000002E-4</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="R20">
-        <v>5.0000000000000001E-4</v>
+        <v>0.11199999999999999</v>
       </c>
       <c r="S20">
-        <v>1.6000000000000001E-4</v>
+        <v>0.108</v>
       </c>
       <c r="T20">
-        <v>0.98</v>
+        <v>0.02</v>
       </c>
       <c r="U20">
+        <v>0.04</v>
+      </c>
+      <c r="V20">
+        <v>0.05</v>
+      </c>
+      <c r="W20">
+        <v>1.6E-2</v>
+      </c>
+      <c r="X20">
+        <v>98</v>
+      </c>
+      <c r="Y20">
+        <v>1.6E-2</v>
+      </c>
+      <c r="Z20">
         <v>55</v>
       </c>
-      <c r="V20">
+      <c r="AA20">
         <v>351</v>
       </c>
-      <c r="W20">
+      <c r="AB20">
         <v>0.86</v>
       </c>
-      <c r="X20">
+      <c r="AC20">
         <v>0.18905232558139534</v>
       </c>
-      <c r="Y20">
+      <c r="AD20">
+        <v>378.10465116279067</v>
+      </c>
+      <c r="AE20">
         <v>8.845200000000001E-3</v>
       </c>
-      <c r="Z20">
+      <c r="AF20">
+        <v>17.6904</v>
+      </c>
+      <c r="AG20">
         <v>6</v>
       </c>
-      <c r="AA20">
+      <c r="AH20">
         <v>1.61E-2</v>
       </c>
-      <c r="AB20">
+      <c r="AI20">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="AJ20">
         <v>0.21399752558139534</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK20">
+        <v>427.99505116279067</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>53</v>
       </c>
       <c r="C21" t="s">
         <v>107</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.18847999999999998</v>
       </c>
-      <c r="E21">
+      <c r="F21">
+        <v>376.96</v>
+      </c>
+      <c r="G21">
         <v>6000</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
       <c r="H21">
+        <v>6000</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>5999.9999994024811</v>
+      </c>
+      <c r="L21">
         <v>5.9999999957536E-2</v>
       </c>
-      <c r="I21">
+      <c r="M21">
         <v>22.617599983992768</v>
       </c>
-      <c r="J21">
-        <v>2E-3</v>
-      </c>
-      <c r="K21">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="L21">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="M21">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="N21">
-        <v>1E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O21">
-        <v>1.1999999999999999E-3</v>
+        <v>0.6</v>
       </c>
       <c r="P21">
-        <v>2.0000000000000001E-4</v>
+        <v>0.5</v>
       </c>
       <c r="Q21">
-        <v>2.0000000000000001E-4</v>
+        <v>0.13</v>
       </c>
       <c r="R21">
-        <v>2.9999999999999997E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S21">
-        <v>1E-4</v>
+        <v>0.12</v>
       </c>
       <c r="T21">
-        <v>0.98</v>
+        <v>0.02</v>
       </c>
       <c r="U21">
+        <v>0.02</v>
+      </c>
+      <c r="V21">
+        <v>0.03</v>
+      </c>
+      <c r="W21">
+        <v>0.01</v>
+      </c>
+      <c r="X21">
+        <v>98</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
         <v>129.13999999999999</v>
       </c>
-      <c r="V21">
+      <c r="AA21">
         <v>318</v>
       </c>
-      <c r="W21">
+      <c r="AB21">
         <v>0.94</v>
       </c>
-      <c r="X21">
+      <c r="AC21">
         <v>0.20051063829787236</v>
       </c>
-      <c r="Y21">
+      <c r="AD21">
+        <v>401.02127659574472</v>
+      </c>
+      <c r="AE21">
         <v>8.0136000000000009E-3</v>
       </c>
-      <c r="Z21">
+      <c r="AF21">
+        <v>16.027200000000001</v>
+      </c>
+      <c r="AG21">
         <v>3</v>
       </c>
-      <c r="AA21">
+      <c r="AH21">
         <v>1.43E-2</v>
       </c>
-      <c r="AB21">
+      <c r="AI21">
+        <v>28.6</v>
+      </c>
+      <c r="AJ21">
         <v>0.22282423829787235</v>
       </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK21">
+        <v>445.64847659574468</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>54</v>
       </c>
       <c r="C22" t="s">
         <v>108</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.17955500000000002</v>
       </c>
-      <c r="E22">
+      <c r="F22">
+        <v>359.11</v>
+      </c>
+      <c r="G22">
         <v>1000</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
       <c r="H22">
+        <v>1000</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>661.25216240885231</v>
+      </c>
+      <c r="L22">
         <v>6.6125216200671397E-3</v>
       </c>
-      <c r="I22">
+      <c r="M22">
         <v>2.3746226389823111</v>
       </c>
-      <c r="J22">
-        <v>0.01</v>
-      </c>
-      <c r="K22">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="L22">
-        <v>8.6700000000000006E-3</v>
-      </c>
-      <c r="M22">
-        <v>1.9E-3</v>
-      </c>
       <c r="N22">
-        <v>1.1199999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="O22">
-        <v>1.08E-3</v>
+        <v>0.6</v>
       </c>
       <c r="P22">
-        <v>3.0000000000000001E-3</v>
+        <v>0.8670000000000001</v>
       </c>
       <c r="Q22">
-        <v>5.0000000000000001E-4</v>
+        <v>0.19</v>
       </c>
       <c r="R22">
-        <v>1E-3</v>
+        <v>0.11199999999999999</v>
       </c>
       <c r="S22">
-        <v>1.6000000000000001E-4</v>
+        <v>0.108</v>
       </c>
       <c r="T22">
-        <v>0.95</v>
+        <v>0.3</v>
       </c>
       <c r="U22">
+        <v>0.05</v>
+      </c>
+      <c r="V22">
+        <v>0.1</v>
+      </c>
+      <c r="W22">
+        <v>1.6E-2</v>
+      </c>
+      <c r="X22">
+        <v>95</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
         <v>132.26</v>
       </c>
-      <c r="V22">
+      <c r="AA22">
         <v>345</v>
       </c>
-      <c r="W22">
+      <c r="AB22">
         <v>0.88</v>
       </c>
-      <c r="X22">
+      <c r="AC22">
         <v>0.20403977272727275</v>
       </c>
-      <c r="Y22">
+      <c r="AD22">
+        <v>408.0795454545455</v>
+      </c>
+      <c r="AE22">
         <v>8.6940000000000003E-3</v>
       </c>
-      <c r="Z22">
+      <c r="AF22">
+        <v>17.388000000000002</v>
+      </c>
+      <c r="AG22">
         <v>3</v>
       </c>
-      <c r="AA22">
+      <c r="AH22">
         <v>1.43E-2</v>
       </c>
-      <c r="AB22">
+      <c r="AI22">
+        <v>28.6</v>
+      </c>
+      <c r="AJ22">
         <v>0.22703377272727274</v>
       </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK22">
+        <v>454.0675454545455</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>55</v>
       </c>
       <c r="C23" t="s">
         <v>109</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.224</v>
       </c>
-      <c r="E23">
+      <c r="F23">
+        <v>448</v>
+      </c>
+      <c r="G23">
         <v>1000</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
       <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J23">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>7.8600000000000007E-3</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>1.4599999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>1.1900000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="O23">
-        <v>1.0300000000000001E-3</v>
+        <v>0.6</v>
       </c>
       <c r="P23">
-        <v>2.9999999999999997E-4</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="Q23">
-        <v>5.0000000000000001E-4</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="R23">
-        <v>1E-3</v>
+        <v>0.11900000000000001</v>
       </c>
       <c r="S23">
-        <v>1.7000000000000001E-4</v>
+        <v>0.10300000000000001</v>
       </c>
       <c r="T23">
-        <v>0.95</v>
+        <v>0.03</v>
       </c>
       <c r="U23">
+        <v>0.05</v>
+      </c>
+      <c r="V23">
+        <v>0.1</v>
+      </c>
+      <c r="W23">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="X23">
+        <v>95</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
         <v>74.867999999999995</v>
       </c>
-      <c r="V23">
+      <c r="AA23">
         <v>365</v>
       </c>
-      <c r="W23">
+      <c r="AB23">
         <v>0.88</v>
       </c>
-      <c r="X23">
+      <c r="AC23">
         <v>0.25454545454545457</v>
       </c>
-      <c r="Y23">
+      <c r="AD23">
+        <v>509.09090909090912</v>
+      </c>
+      <c r="AE23">
         <v>9.1979999999999996E-3</v>
       </c>
-      <c r="Z23">
+      <c r="AF23">
+        <v>18.396000000000001</v>
+      </c>
+      <c r="AG23">
         <v>3</v>
       </c>
-      <c r="AA23">
+      <c r="AH23">
         <v>1.43E-2</v>
       </c>
-      <c r="AB23">
+      <c r="AI23">
+        <v>28.6</v>
+      </c>
+      <c r="AJ23">
         <v>0.27804345454545454</v>
       </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK23">
+        <v>556.0869090909091</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>56</v>
       </c>
       <c r="C24" t="s">
         <v>110</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>0.20805500000000002</v>
       </c>
-      <c r="E24">
+      <c r="F24">
+        <v>416.11</v>
+      </c>
+      <c r="G24">
         <v>1000</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
       <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J24">
-        <v>2.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>2.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>6.1999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>1.1999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>5.9999999999999995E-4</v>
+        <v>0.25</v>
       </c>
       <c r="O24">
-        <v>5.9999999999999995E-4</v>
+        <v>0.25</v>
       </c>
       <c r="P24">
-        <v>1E-4</v>
+        <v>0.62</v>
       </c>
       <c r="Q24">
-        <v>2.0000000000000001E-4</v>
+        <v>0.12</v>
       </c>
       <c r="R24">
-        <v>4.4999999999999999E-4</v>
+        <v>0.06</v>
       </c>
       <c r="S24">
-        <v>4.0000000000000002E-4</v>
+        <v>0.06</v>
       </c>
       <c r="T24">
-        <v>0.95</v>
+        <v>0.01</v>
       </c>
       <c r="U24">
+        <v>0.02</v>
+      </c>
+      <c r="V24">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="W24">
+        <v>0.04</v>
+      </c>
+      <c r="X24">
+        <v>95</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
         <v>119.16</v>
       </c>
-      <c r="V24">
+      <c r="AA24">
         <v>350</v>
       </c>
-      <c r="W24">
+      <c r="AB24">
         <v>0.75</v>
       </c>
-      <c r="X24">
+      <c r="AC24">
         <v>0.27740666666666669</v>
       </c>
-      <c r="Y24">
+      <c r="AD24">
+        <v>554.81333333333339</v>
+      </c>
+      <c r="AE24">
         <v>8.8199999999999997E-3</v>
       </c>
-      <c r="Z24">
+      <c r="AF24">
+        <v>17.64</v>
+      </c>
+      <c r="AG24">
         <v>7</v>
       </c>
-      <c r="AA24">
+      <c r="AH24">
         <v>1.67E-2</v>
       </c>
-      <c r="AB24">
+      <c r="AI24">
+        <v>33.4</v>
+      </c>
+      <c r="AJ24">
         <v>0.30292666666666668</v>
       </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK24">
+        <v>605.85333333333335</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -2786,180 +3396,228 @@
       <c r="C25" t="s">
         <v>111</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25">
         <v>0.16798500000000002</v>
       </c>
-      <c r="E25">
+      <c r="F25">
+        <v>335.97</v>
+      </c>
+      <c r="G25">
         <v>2000</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
       <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J25">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>5.9999999999999995E-4</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>1.5E-3</v>
+        <v>0.3</v>
       </c>
       <c r="O25">
-        <v>1.1999999999999999E-3</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="P25">
-        <v>1.5E-3</v>
+        <v>0.06</v>
       </c>
       <c r="Q25">
-        <v>4.0000000000000002E-4</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="R25">
-        <v>4.4999999999999999E-4</v>
+        <v>0.15</v>
       </c>
       <c r="S25">
-        <v>2.9999999999999997E-4</v>
+        <v>0.12</v>
       </c>
       <c r="T25">
-        <v>0.96</v>
+        <v>0.15</v>
       </c>
       <c r="U25">
+        <v>0.04</v>
+      </c>
+      <c r="V25">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="W25">
+        <v>0.03</v>
+      </c>
+      <c r="X25">
+        <v>96</v>
+      </c>
+      <c r="Y25">
+        <v>0.03</v>
+      </c>
+      <c r="Z25">
         <v>44.92</v>
       </c>
-      <c r="V25">
+      <c r="AA25">
         <v>350</v>
       </c>
-      <c r="W25">
+      <c r="AB25">
         <v>0.86</v>
       </c>
-      <c r="X25">
+      <c r="AC25">
         <v>0.1953313953488372</v>
       </c>
-      <c r="Y25">
+      <c r="AD25">
+        <v>390.66279069767438</v>
+      </c>
+      <c r="AE25">
         <v>8.8199999999999997E-3</v>
       </c>
-      <c r="Z25">
+      <c r="AF25">
+        <v>17.64</v>
+      </c>
+      <c r="AG25">
         <v>5</v>
       </c>
-      <c r="AA25">
+      <c r="AH25">
         <v>1.55E-2</v>
       </c>
-      <c r="AB25">
+      <c r="AI25">
+        <v>31</v>
+      </c>
+      <c r="AJ25">
         <v>0.21965139534883721</v>
       </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK25">
+        <v>439.30279069767442</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>58</v>
       </c>
       <c r="C26" t="s">
         <v>112</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26">
         <v>0.14438999999999999</v>
       </c>
-      <c r="E26">
+      <c r="F26">
+        <v>288.77999999999997</v>
+      </c>
+      <c r="G26">
         <v>1000</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
       <c r="H26">
+        <v>1000</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>1000</v>
+      </c>
+      <c r="L26">
         <v>9.9999999939185315E-3</v>
       </c>
-      <c r="I26">
+      <c r="M26">
         <v>2.8877999982437932</v>
       </c>
-      <c r="J26">
-        <v>3.6000000000000002E-4</v>
-      </c>
-      <c r="K26">
-        <v>2E-3</v>
-      </c>
-      <c r="L26">
-        <v>3.5000000000000001E-3</v>
-      </c>
-      <c r="M26">
-        <v>1.1000000000000001E-3</v>
-      </c>
       <c r="N26">
-        <v>6.9999999999999999E-4</v>
+        <v>3.6000000000000004E-2</v>
       </c>
       <c r="O26">
-        <v>6.9999999999999999E-4</v>
+        <v>0.2</v>
       </c>
       <c r="P26">
-        <v>1E-4</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="Q26">
-        <v>1E-4</v>
+        <v>0.11</v>
       </c>
       <c r="R26">
-        <v>5.1999999999999995E-4</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="S26">
-        <v>2.0000000000000001E-4</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="T26">
-        <v>0.94</v>
+        <v>0.01</v>
       </c>
       <c r="U26">
+        <v>0.01</v>
+      </c>
+      <c r="V26">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="W26">
+        <v>0.02</v>
+      </c>
+      <c r="X26">
+        <v>94</v>
+      </c>
+      <c r="Y26">
+        <v>0.02</v>
+      </c>
+      <c r="Z26">
         <v>150</v>
       </c>
-      <c r="V26">
+      <c r="AA26">
         <v>404</v>
       </c>
-      <c r="W26">
+      <c r="AB26">
         <v>0.85</v>
       </c>
-      <c r="X26">
+      <c r="AC26">
         <v>0.16987058823529411</v>
       </c>
-      <c r="Y26">
+      <c r="AD26">
+        <v>339.74117647058819</v>
+      </c>
+      <c r="AE26">
         <v>1.01808E-2</v>
       </c>
-      <c r="Z26">
+      <c r="AF26">
+        <v>20.361599999999999</v>
+      </c>
+      <c r="AG26">
         <v>10</v>
       </c>
-      <c r="AA26">
+      <c r="AH26">
         <v>1.8499999999999999E-2</v>
       </c>
-      <c r="AB26">
+      <c r="AI26">
+        <v>37</v>
+      </c>
+      <c r="AJ26">
         <v>0.19855138823529409</v>
       </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK26">
+        <v>397.1027764705882</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>59</v>
       </c>
       <c r="C27" t="s">
         <v>113</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27">
         <v>0.14629499999999998</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
       <c r="F27">
-        <v>0</v>
+        <v>292.58999999999997</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -2967,82 +3625,106 @@
       <c r="H27">
         <v>0</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
       <c r="J27">
-        <v>4.0000000000000002E-4</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>3.7000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>6.6E-3</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>1.1000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>2.5999999999999998E-4</v>
+        <v>0.04</v>
       </c>
       <c r="O27">
-        <v>4.4999999999999999E-4</v>
+        <v>0.37</v>
       </c>
       <c r="P27">
-        <v>3.0000000000000001E-5</v>
+        <v>0.66</v>
       </c>
       <c r="Q27">
-        <v>5.9999999999999995E-4</v>
+        <v>0.11</v>
       </c>
       <c r="R27">
-        <v>2.7E-4</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="S27">
-        <v>2.0000000000000001E-4</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="T27">
-        <v>0.9</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U27">
+        <v>0.06</v>
+      </c>
+      <c r="V27">
+        <v>2.7E-2</v>
+      </c>
+      <c r="W27">
+        <v>0.02</v>
+      </c>
+      <c r="X27">
+        <v>90</v>
+      </c>
+      <c r="Y27">
+        <v>0.02</v>
+      </c>
+      <c r="Z27">
         <v>100</v>
       </c>
-      <c r="V27">
+      <c r="AA27">
         <v>404</v>
       </c>
-      <c r="W27">
+      <c r="AB27">
         <v>0.86</v>
       </c>
-      <c r="X27">
+      <c r="AC27">
         <v>0.17011046511627906</v>
       </c>
-      <c r="Y27">
+      <c r="AD27">
+        <v>340.22093023255809</v>
+      </c>
+      <c r="AE27">
         <v>1.01808E-2</v>
       </c>
-      <c r="Z27">
+      <c r="AF27">
+        <v>20.361599999999999</v>
+      </c>
+      <c r="AG27">
         <v>7</v>
       </c>
-      <c r="AA27">
+      <c r="AH27">
         <v>1.67E-2</v>
       </c>
-      <c r="AB27">
+      <c r="AI27">
+        <v>33.4</v>
+      </c>
+      <c r="AJ27">
         <v>0.19699126511627904</v>
       </c>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK27">
+        <v>393.98253023255808</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>60</v>
       </c>
       <c r="C28" t="s">
         <v>114</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="s">
+        <v>141</v>
+      </c>
+      <c r="E28">
         <v>0.16869000000000001</v>
       </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
       <c r="F28">
-        <v>0</v>
+        <v>337.38</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3050,82 +3732,103 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
       <c r="J28">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>2.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>1.1999999999999999E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O28">
-        <v>1.4E-3</v>
+        <v>0.2</v>
       </c>
       <c r="P28">
-        <v>2.0000000000000001E-4</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="Q28">
-        <v>2.9999999999999997E-4</v>
+        <v>0.25</v>
       </c>
       <c r="R28">
-        <v>5.0000000000000001E-4</v>
+        <v>0.12</v>
       </c>
       <c r="S28">
-        <v>2.9999999999999997E-4</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="T28">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="U28">
+        <v>0.03</v>
+      </c>
+      <c r="V28">
+        <v>0.05</v>
+      </c>
+      <c r="W28">
+        <v>0.03</v>
+      </c>
+      <c r="X28">
+        <v>95</v>
+      </c>
+      <c r="Y28">
+        <v>0.03</v>
+      </c>
+      <c r="Z28">
         <v>69.87</v>
       </c>
-      <c r="V28">
+      <c r="AA28">
         <v>264</v>
       </c>
-      <c r="W28">
+      <c r="AB28">
         <v>0.86</v>
       </c>
-      <c r="X28">
+      <c r="AC28">
         <v>0.19615116279069764</v>
       </c>
-      <c r="Y28">
+      <c r="AD28">
+        <v>392.30232558139528</v>
+      </c>
+      <c r="AE28">
         <v>6.6528000000000004E-3</v>
       </c>
-      <c r="Z28">
+      <c r="AF28">
+        <v>13.3056</v>
+      </c>
+      <c r="AG28">
         <v>5</v>
       </c>
-      <c r="AA28">
+      <c r="AH28">
         <v>1.55E-2</v>
       </c>
-      <c r="AB28">
+      <c r="AI28">
+        <v>31</v>
+      </c>
+      <c r="AJ28">
         <v>0.21830396279069772</v>
       </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK28">
+        <v>436.60792558139542</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>61</v>
       </c>
       <c r="C29" t="s">
         <v>115</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>0.22975999999999999</v>
       </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
       <c r="F29">
-        <v>0</v>
+        <v>459.52</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3133,151 +3836,199 @@
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
       <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>2</v>
+      </c>
+      <c r="O29">
+        <v>0.3</v>
+      </c>
+      <c r="P29">
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="Q29">
+        <v>0.2</v>
+      </c>
+      <c r="R29">
+        <v>0.2</v>
+      </c>
+      <c r="S29">
+        <v>0.1</v>
+      </c>
+      <c r="T29">
         <v>0.02</v>
       </c>
-      <c r="K29">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="L29">
-        <v>3.5000000000000001E-3</v>
-      </c>
-      <c r="M29">
-        <v>2E-3</v>
-      </c>
-      <c r="N29">
-        <v>2E-3</v>
-      </c>
-      <c r="O29">
-        <v>1E-3</v>
-      </c>
-      <c r="P29">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="Q29">
-        <v>3.5E-4</v>
-      </c>
-      <c r="R29">
-        <v>1.5E-3</v>
-      </c>
-      <c r="S29">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="T29">
-        <v>0.96</v>
-      </c>
       <c r="U29">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.02</v>
+      </c>
+      <c r="X29">
+        <v>96</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
         <v>132.26</v>
       </c>
-      <c r="V29">
+      <c r="AA29">
         <v>345</v>
       </c>
-      <c r="W29">
+      <c r="AB29">
         <v>0.87</v>
       </c>
-      <c r="X29">
+      <c r="AC29">
         <v>0.26409195402298846</v>
       </c>
-      <c r="Y29">
+      <c r="AD29">
+        <v>528.18390804597698</v>
+      </c>
+      <c r="AE29">
         <v>8.6940000000000003E-3</v>
       </c>
-      <c r="Z29">
+      <c r="AF29">
+        <v>17.388000000000002</v>
+      </c>
+      <c r="AG29">
         <v>5</v>
       </c>
-      <c r="AA29">
+      <c r="AH29">
         <v>1.55E-2</v>
       </c>
-      <c r="AB29">
+      <c r="AI29">
+        <v>31</v>
+      </c>
+      <c r="AJ29">
         <v>0.28828595402298851</v>
       </c>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK29">
+        <v>576.57190804597701</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>62</v>
       </c>
       <c r="C30" t="s">
         <v>116</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30">
         <v>0.165855</v>
       </c>
-      <c r="E30">
+      <c r="F30">
+        <v>331.71</v>
+      </c>
+      <c r="G30">
         <v>1000</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
       <c r="H30">
+        <v>1000</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>1000</v>
+      </c>
+      <c r="L30">
         <v>9.9999999939185315E-3</v>
       </c>
-      <c r="I30">
+      <c r="M30">
         <v>3.3170999979827158</v>
       </c>
-      <c r="J30">
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30">
+        <v>0.3</v>
+      </c>
+      <c r="P30">
+        <v>0.65</v>
+      </c>
+      <c r="Q30">
+        <v>0.12</v>
+      </c>
+      <c r="R30">
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="S30">
+        <v>0.08</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
         <v>0.02</v>
       </c>
-      <c r="K30">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="L30">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="M30">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="N30">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="O30">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="T30">
-        <v>0.96</v>
-      </c>
-      <c r="U30">
+      <c r="X30">
+        <v>96</v>
+      </c>
+      <c r="Y30">
+        <v>0.02</v>
+      </c>
+      <c r="Z30">
         <v>132.26</v>
       </c>
-      <c r="V30">
+      <c r="AA30">
         <v>345</v>
       </c>
-      <c r="W30">
+      <c r="AB30">
         <v>0.92</v>
       </c>
-      <c r="X30">
+      <c r="AC30">
         <v>0.18027717391304343</v>
       </c>
-      <c r="Y30">
+      <c r="AD30">
+        <v>360.55434782608688</v>
+      </c>
+      <c r="AE30">
         <v>8.6940000000000003E-3</v>
       </c>
-      <c r="Z30">
+      <c r="AF30">
+        <v>17.388000000000002</v>
+      </c>
+      <c r="AG30">
         <v>3</v>
       </c>
-      <c r="AA30">
+      <c r="AH30">
         <v>1.43E-2</v>
       </c>
-      <c r="AB30">
+      <c r="AI30">
+        <v>28.6</v>
+      </c>
+      <c r="AJ30">
         <v>0.20327117391304345</v>
       </c>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK30">
+        <v>406.54234782608688</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -3287,14 +4038,11 @@
       <c r="C31" t="s">
         <v>117</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>0.25</v>
       </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
       <c r="F31">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3302,82 +4050,103 @@
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
       <c r="J31">
-        <v>6.2E-4</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>1.2999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>4.1999999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>2.5000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>3.4000000000000002E-4</v>
+        <v>6.2E-2</v>
       </c>
       <c r="O31">
-        <v>1.4800000000000001E-2</v>
+        <v>0.13</v>
       </c>
       <c r="P31">
-        <v>9.6000000000000002E-5</v>
+        <v>0.42</v>
       </c>
       <c r="Q31">
-        <v>1E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="R31">
-        <v>2.04E-4</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="S31">
-        <v>2.7999999999999998E-4</v>
+        <v>1.48</v>
       </c>
       <c r="T31">
-        <v>0.98199999999999998</v>
+        <v>9.6000000000000009E-3</v>
       </c>
       <c r="U31">
+        <v>0.1</v>
+      </c>
+      <c r="V31">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="W31">
+        <v>2.7999999999999997E-2</v>
+      </c>
+      <c r="X31">
+        <v>98.2</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
         <v>200</v>
       </c>
-      <c r="V31">
+      <c r="AA31">
         <v>304</v>
       </c>
-      <c r="W31">
+      <c r="AB31">
         <v>0.88</v>
       </c>
-      <c r="X31">
+      <c r="AC31">
         <v>0.28409090909090906</v>
       </c>
-      <c r="Y31">
+      <c r="AD31">
+        <v>568.18181818181813</v>
+      </c>
+      <c r="AE31">
         <v>7.6607999999999997E-3</v>
       </c>
-      <c r="Z31">
+      <c r="AF31">
+        <v>15.3216</v>
+      </c>
+      <c r="AG31">
         <v>4</v>
       </c>
-      <c r="AA31">
+      <c r="AH31">
         <v>1.49E-2</v>
       </c>
-      <c r="AB31">
+      <c r="AI31">
+        <v>29.8</v>
+      </c>
+      <c r="AJ31">
         <v>0.30665170909090905</v>
       </c>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK31">
+        <v>613.30341818181807</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>64</v>
       </c>
       <c r="C32" t="s">
         <v>118</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>0.25</v>
       </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
       <c r="F32">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3385,82 +4154,103 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
       <c r="J32">
-        <v>2.9999999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>5.9000000000000003E-4</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>9.5499999999999995E-3</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>2.4800000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>2.2499999999999999E-4</v>
+        <v>0.03</v>
       </c>
       <c r="O32">
-        <v>0.01</v>
+        <v>5.9000000000000004E-2</v>
       </c>
       <c r="P32">
-        <v>6.3999999999999997E-5</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="Q32">
-        <v>1E-3</v>
+        <v>2.4800000000000003E-2</v>
       </c>
       <c r="R32">
-        <v>1.0499999999999999E-3</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="S32">
-        <v>2.1000000000000001E-4</v>
+        <v>1</v>
       </c>
       <c r="T32">
-        <v>0.98199999999999998</v>
+        <v>6.3999999999999994E-3</v>
       </c>
       <c r="U32">
+        <v>0.1</v>
+      </c>
+      <c r="V32">
+        <v>0.105</v>
+      </c>
+      <c r="W32">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="X32">
+        <v>98.2</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
         <v>70</v>
       </c>
-      <c r="V32">
+      <c r="AA32">
         <v>322</v>
       </c>
-      <c r="W32">
+      <c r="AB32">
         <v>0.88</v>
       </c>
-      <c r="X32">
+      <c r="AC32">
         <v>0.28409090909090906</v>
       </c>
-      <c r="Y32">
+      <c r="AD32">
+        <v>568.18181818181813</v>
+      </c>
+      <c r="AE32">
         <v>8.114399999999999E-3</v>
       </c>
-      <c r="Z32">
+      <c r="AF32">
+        <v>16.2288</v>
+      </c>
+      <c r="AG32">
         <v>4</v>
       </c>
-      <c r="AA32">
+      <c r="AH32">
         <v>1.49E-2</v>
       </c>
-      <c r="AB32">
+      <c r="AI32">
+        <v>29.8</v>
+      </c>
+      <c r="AJ32">
         <v>0.30710530909090905</v>
       </c>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK32">
+        <v>614.21061818181806</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>65</v>
       </c>
       <c r="C33" t="s">
         <v>119</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>0.25</v>
       </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
       <c r="F33">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3468,82 +4258,106 @@
       <c r="H33">
         <v>0</v>
       </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
       <c r="J33">
-        <v>5.9999999999999995E-4</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>5.0000000000000002E-5</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>8.8999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>2.7999999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>2.5700000000000001E-4</v>
+        <v>0.06</v>
       </c>
       <c r="O33">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P33">
+        <v>0.89</v>
+      </c>
+      <c r="Q33">
+        <v>2.7999999999999997E-2</v>
+      </c>
+      <c r="R33">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="S33">
+        <v>1.49</v>
+      </c>
+      <c r="T33">
+        <v>6.9999999999999993E-3</v>
+      </c>
+      <c r="U33">
+        <v>0.1</v>
+      </c>
+      <c r="V33">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="W33">
+        <v>1E-3</v>
+      </c>
+      <c r="X33">
+        <v>98.2</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>200</v>
+      </c>
+      <c r="AA33">
+        <v>304</v>
+      </c>
+      <c r="AB33">
+        <v>0.88</v>
+      </c>
+      <c r="AC33">
+        <v>0.28409090909090906</v>
+      </c>
+      <c r="AD33">
+        <v>568.18181818181813</v>
+      </c>
+      <c r="AE33">
+        <v>7.6607999999999997E-3</v>
+      </c>
+      <c r="AF33">
+        <v>15.3216</v>
+      </c>
+      <c r="AG33">
+        <v>4</v>
+      </c>
+      <c r="AH33">
         <v>1.49E-2</v>
       </c>
-      <c r="P33">
-        <v>6.9999999999999994E-5</v>
-      </c>
-      <c r="Q33">
-        <v>1E-3</v>
-      </c>
-      <c r="R33">
-        <v>1.7000000000000001E-4</v>
-      </c>
-      <c r="S33">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="T33">
-        <v>0.98199999999999998</v>
-      </c>
-      <c r="U33">
-        <v>200</v>
-      </c>
-      <c r="V33">
-        <v>304</v>
-      </c>
-      <c r="W33">
-        <v>0.88</v>
-      </c>
-      <c r="X33">
-        <v>0.28409090909090906</v>
-      </c>
-      <c r="Y33">
-        <v>7.6607999999999997E-3</v>
-      </c>
-      <c r="Z33">
-        <v>4</v>
-      </c>
-      <c r="AA33">
-        <v>1.49E-2</v>
-      </c>
-      <c r="AB33">
+      <c r="AI33">
+        <v>29.8</v>
+      </c>
+      <c r="AJ33">
         <v>0.30665170909090905</v>
       </c>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK33">
+        <v>613.30341818181807</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>66</v>
       </c>
       <c r="C34" t="s">
         <v>120</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34">
         <v>0.20805500000000002</v>
       </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
       <c r="F34">
-        <v>0</v>
+        <v>416.11</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -3551,68 +4365,92 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
       <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0.8</v>
+      </c>
+      <c r="O34">
+        <v>0.32</v>
+      </c>
+      <c r="P34">
+        <v>0.75</v>
+      </c>
+      <c r="Q34">
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="R34">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="S34">
+        <v>0.88</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="K34">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="L34">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="M34">
-        <v>2.8E-3</v>
-      </c>
-      <c r="N34">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="O34">
-        <v>8.8000000000000005E-3</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="R34">
-        <v>2.1000000000000001E-4</v>
-      </c>
-      <c r="S34">
-        <v>2.8E-3</v>
-      </c>
-      <c r="T34">
-        <v>0.96</v>
-      </c>
-      <c r="U34">
+      <c r="V34">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="W34">
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="X34">
+        <v>96</v>
+      </c>
+      <c r="Y34">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Z34">
         <v>200</v>
       </c>
-      <c r="V34">
+      <c r="AA34">
         <v>318</v>
       </c>
-      <c r="W34">
+      <c r="AB34">
         <v>0.95</v>
       </c>
-      <c r="X34">
+      <c r="AC34">
         <v>0.21900526315789476</v>
       </c>
-      <c r="Y34">
+      <c r="AD34">
+        <v>438.01052631578949</v>
+      </c>
+      <c r="AE34">
         <v>8.0136000000000009E-3</v>
       </c>
-      <c r="Z34">
+      <c r="AF34">
+        <v>16.027200000000001</v>
+      </c>
+      <c r="AG34">
         <v>2</v>
       </c>
-      <c r="AA34">
+      <c r="AH34">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="AB34">
+      <c r="AI34">
+        <v>27.4</v>
+      </c>
+      <c r="AJ34">
         <v>0.24071886315789476</v>
       </c>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK34">
+        <v>481.43772631578952</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -3622,14 +4460,11 @@
       <c r="C35" t="s">
         <v>121</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>0.1925</v>
       </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
       <c r="F35">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -3637,165 +4472,213 @@
       <c r="H35">
         <v>0</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
       <c r="J35">
-        <v>1.95E-2</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>4.1000000000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>9.5999999999999992E-3</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>2.3E-3</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>1.9499999999999999E-3</v>
+        <v>1.95</v>
       </c>
       <c r="O35">
-        <v>1.1000000000000001E-3</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="P35">
-        <v>2.0000000000000001E-4</v>
+        <v>0.96</v>
       </c>
       <c r="Q35">
-        <v>2.0000000000000001E-4</v>
+        <v>0.22999999999999998</v>
       </c>
       <c r="R35">
-        <v>2.6999999999999999E-5</v>
+        <v>0.19499999999999998</v>
       </c>
       <c r="S35">
-        <v>6.4999999999999997E-4</v>
+        <v>0.11</v>
       </c>
       <c r="T35">
-        <v>0.85</v>
+        <v>0.02</v>
       </c>
       <c r="U35">
+        <v>0.02</v>
+      </c>
+      <c r="V35">
+        <v>2.6999999999999997E-3</v>
+      </c>
+      <c r="W35">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="X35">
+        <v>85</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
         <v>167.38</v>
       </c>
-      <c r="V35">
+      <c r="AA35">
         <v>500</v>
       </c>
-      <c r="W35">
+      <c r="AB35">
         <v>0.75</v>
       </c>
-      <c r="X35">
+      <c r="AC35">
         <v>0.25666666666666671</v>
       </c>
-      <c r="Y35">
+      <c r="AD35">
+        <v>513.33333333333337</v>
+      </c>
+      <c r="AE35">
         <v>1.26E-2</v>
       </c>
-      <c r="Z35">
+      <c r="AF35">
+        <v>25.2</v>
+      </c>
+      <c r="AG35">
         <v>8</v>
       </c>
-      <c r="AA35">
+      <c r="AH35">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="AB35">
+      <c r="AI35">
+        <v>34.6</v>
+      </c>
+      <c r="AJ35">
         <v>0.28656666666666675</v>
       </c>
-    </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK35">
+        <v>573.13333333333344</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>68</v>
       </c>
       <c r="C36" t="s">
         <v>122</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36">
         <v>0.16711999999999999</v>
       </c>
-      <c r="E36">
+      <c r="F36">
+        <v>334.24</v>
+      </c>
+      <c r="G36">
         <v>1000</v>
       </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
       <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J36">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L36">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>1E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O36">
-        <v>1.1999999999999999E-3</v>
+        <v>0.3</v>
       </c>
       <c r="P36">
-        <v>2.0000000000000001E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q36">
-        <v>4.0000000000000002E-4</v>
+        <v>0.2</v>
       </c>
       <c r="R36">
-        <v>2.9999999999999997E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S36">
-        <v>2.9999999999999997E-4</v>
+        <v>0.12</v>
       </c>
       <c r="T36">
-        <v>0.85</v>
+        <v>0.02</v>
       </c>
       <c r="U36">
+        <v>0.04</v>
+      </c>
+      <c r="V36">
+        <v>0.03</v>
+      </c>
+      <c r="W36">
+        <v>0.03</v>
+      </c>
+      <c r="X36">
+        <v>85</v>
+      </c>
+      <c r="Y36">
+        <v>0.03</v>
+      </c>
+      <c r="Z36">
         <v>119.78</v>
       </c>
-      <c r="V36">
+      <c r="AA36">
         <v>415</v>
       </c>
-      <c r="W36">
+      <c r="AB36">
         <v>0.74</v>
       </c>
-      <c r="X36">
+      <c r="AC36">
         <v>0.22583783783783784</v>
       </c>
-      <c r="Y36">
+      <c r="AD36">
+        <v>451.67567567567568</v>
+      </c>
+      <c r="AE36">
         <v>1.0458E-2</v>
       </c>
-      <c r="Z36">
+      <c r="AF36">
+        <v>20.916</v>
+      </c>
+      <c r="AG36">
         <v>8</v>
       </c>
-      <c r="AA36">
+      <c r="AH36">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="AB36">
+      <c r="AI36">
+        <v>34.6</v>
+      </c>
+      <c r="AJ36">
         <v>0.25359583783783785</v>
       </c>
-    </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK36">
+        <v>507.1916756756757</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>69</v>
       </c>
       <c r="C37" t="s">
         <v>123</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="s">
+        <v>138</v>
+      </c>
+      <c r="E37">
         <v>0.15062500000000001</v>
       </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
       <c r="F37">
-        <v>0</v>
+        <v>301.25</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -3803,400 +4686,517 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
       <c r="J37">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L37">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>1.8E-3</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>1E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O37">
-        <v>1.1999999999999999E-3</v>
+        <v>0.3</v>
       </c>
       <c r="P37">
-        <v>2.0000000000000001E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q37">
-        <v>4.0000000000000002E-4</v>
+        <v>0.18</v>
       </c>
       <c r="R37">
-        <v>2.9999999999999997E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S37">
-        <v>2.9999999999999997E-4</v>
+        <v>0.12</v>
       </c>
       <c r="T37">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="U37">
+        <v>0.04</v>
+      </c>
+      <c r="V37">
+        <v>0.03</v>
+      </c>
+      <c r="W37">
+        <v>0.03</v>
+      </c>
+      <c r="X37">
+        <v>95</v>
+      </c>
+      <c r="Y37">
+        <v>0.03</v>
+      </c>
+      <c r="Z37">
         <v>489</v>
       </c>
-      <c r="V37">
+      <c r="AA37">
         <v>387</v>
       </c>
-      <c r="W37">
+      <c r="AB37">
         <v>0.88</v>
       </c>
-      <c r="X37">
+      <c r="AC37">
         <v>0.17116477272727268</v>
       </c>
-      <c r="Y37">
+      <c r="AD37">
+        <v>342.32954545454538</v>
+      </c>
+      <c r="AE37">
         <v>9.7523999999999996E-3</v>
       </c>
-      <c r="Z37">
+      <c r="AF37">
+        <v>19.504799999999999</v>
+      </c>
+      <c r="AG37">
         <v>5</v>
       </c>
-      <c r="AA37">
+      <c r="AH37">
         <v>1.55E-2</v>
       </c>
-      <c r="AB37">
+      <c r="AI37">
+        <v>31</v>
+      </c>
+      <c r="AJ37">
         <v>0.19641717272727272</v>
       </c>
-    </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK37">
+        <v>392.83434545454543</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>70</v>
       </c>
       <c r="C38" t="s">
         <v>124</v>
       </c>
-      <c r="D38">
+      <c r="D38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38">
         <v>0.16711999999999999</v>
       </c>
-      <c r="E38">
+      <c r="F38">
+        <v>334.24</v>
+      </c>
+      <c r="G38">
         <v>5000</v>
       </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
       <c r="H38">
+        <v>5000</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>4214.9133464476899</v>
+      </c>
+      <c r="L38">
         <v>4.2149133438844043E-2</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>14.08792636059923</v>
       </c>
-      <c r="J38">
-        <v>2E-3</v>
-      </c>
-      <c r="K38">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="L38">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="M38">
-        <v>2E-3</v>
-      </c>
       <c r="N38">
-        <v>1E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O38">
-        <v>1.1999999999999999E-3</v>
+        <v>0.3</v>
       </c>
       <c r="P38">
-        <v>2.0000000000000001E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q38">
-        <v>4.0000000000000002E-4</v>
+        <v>0.2</v>
       </c>
       <c r="R38">
-        <v>2.9999999999999997E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S38">
-        <v>2.9999999999999997E-4</v>
+        <v>0.12</v>
       </c>
       <c r="T38">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="U38">
+        <v>0.04</v>
+      </c>
+      <c r="V38">
+        <v>0.03</v>
+      </c>
+      <c r="W38">
+        <v>0.03</v>
+      </c>
+      <c r="X38">
+        <v>95</v>
+      </c>
+      <c r="Y38">
+        <v>0.03</v>
+      </c>
+      <c r="Z38">
         <v>119.16</v>
       </c>
-      <c r="V38">
+      <c r="AA38">
         <v>350</v>
       </c>
-      <c r="W38">
+      <c r="AB38">
         <v>0.8</v>
       </c>
-      <c r="X38">
+      <c r="AC38">
         <v>0.2089</v>
       </c>
-      <c r="Y38">
+      <c r="AD38">
+        <v>417.8</v>
+      </c>
+      <c r="AE38">
         <v>8.8199999999999997E-3</v>
       </c>
-      <c r="Z38">
+      <c r="AF38">
+        <v>17.64</v>
+      </c>
+      <c r="AG38">
         <v>6</v>
       </c>
-      <c r="AA38">
+      <c r="AH38">
         <v>1.61E-2</v>
       </c>
-      <c r="AB38">
+      <c r="AI38">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="AJ38">
         <v>0.23382</v>
       </c>
-    </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK38">
+        <v>467.64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>71</v>
       </c>
       <c r="C39" t="s">
         <v>125</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>0.147065</v>
       </c>
-      <c r="E39">
+      <c r="F39">
+        <v>294.13</v>
+      </c>
+      <c r="G39">
         <v>1000</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
       <c r="H39">
+        <v>1000</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>1000</v>
+      </c>
+      <c r="L39">
         <v>9.9999999939185315E-3</v>
       </c>
-      <c r="I39">
+      <c r="M39">
         <v>2.941299998211258</v>
       </c>
-      <c r="J39">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="K39">
-        <v>1.5E-3</v>
-      </c>
-      <c r="L39">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="M39">
-        <v>2E-3</v>
-      </c>
       <c r="N39">
-        <v>5.0000000000000001E-4</v>
+        <v>0.3</v>
       </c>
       <c r="O39">
-        <v>4.0000000000000002E-4</v>
+        <v>0.15</v>
       </c>
       <c r="P39">
-        <v>1E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q39">
-        <v>1E-4</v>
+        <v>0.2</v>
       </c>
       <c r="R39">
-        <v>1E-4</v>
+        <v>0.05</v>
       </c>
       <c r="S39">
-        <v>1E-4</v>
+        <v>0.04</v>
       </c>
       <c r="T39">
-        <v>0.98</v>
+        <v>0.01</v>
       </c>
       <c r="U39">
+        <v>0.01</v>
+      </c>
+      <c r="V39">
+        <v>0.01</v>
+      </c>
+      <c r="W39">
+        <v>0.01</v>
+      </c>
+      <c r="X39">
+        <v>98</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
         <v>119.78</v>
       </c>
-      <c r="V39">
+      <c r="AA39">
         <v>350</v>
       </c>
-      <c r="W39">
+      <c r="AB39">
         <v>0.93</v>
       </c>
-      <c r="X39">
+      <c r="AC39">
         <v>0.15813440860215056</v>
       </c>
-      <c r="Y39">
+      <c r="AD39">
+        <v>316.26881720430111</v>
+      </c>
+      <c r="AE39">
         <v>8.8199999999999997E-3</v>
       </c>
-      <c r="Z39">
+      <c r="AF39">
+        <v>17.64</v>
+      </c>
+      <c r="AG39">
         <v>3</v>
       </c>
-      <c r="AA39">
+      <c r="AH39">
         <v>1.43E-2</v>
       </c>
-      <c r="AB39">
+      <c r="AI39">
+        <v>28.6</v>
+      </c>
+      <c r="AJ39">
         <v>0.18125440860215056</v>
       </c>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK39">
+        <v>362.50881720430112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>72</v>
       </c>
       <c r="C40" t="s">
         <v>126</v>
       </c>
-      <c r="D40">
+      <c r="D40" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40">
         <v>0.147065</v>
       </c>
-      <c r="E40">
+      <c r="F40">
+        <v>294.13</v>
+      </c>
+      <c r="G40">
         <v>1000</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
       <c r="H40">
+        <v>1000</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>1000.000863871761</v>
+      </c>
+      <c r="L40">
         <v>1.0000008632636141E-2</v>
       </c>
-      <c r="I40">
+      <c r="M40">
         <v>2.941302539117268</v>
       </c>
-      <c r="J40">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="K40">
-        <v>1.5E-3</v>
-      </c>
-      <c r="L40">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="M40">
-        <v>1.8E-3</v>
-      </c>
       <c r="N40">
-        <v>5.0000000000000001E-4</v>
+        <v>0.3</v>
       </c>
       <c r="O40">
-        <v>4.0000000000000002E-4</v>
+        <v>0.15</v>
       </c>
       <c r="P40">
-        <v>1E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q40">
-        <v>1E-4</v>
+        <v>0.18</v>
       </c>
       <c r="R40">
-        <v>1E-4</v>
+        <v>0.05</v>
       </c>
       <c r="S40">
-        <v>1E-4</v>
+        <v>0.04</v>
       </c>
       <c r="T40">
-        <v>0.97</v>
+        <v>0.01</v>
       </c>
       <c r="U40">
+        <v>0.01</v>
+      </c>
+      <c r="V40">
+        <v>0.01</v>
+      </c>
+      <c r="W40">
+        <v>0.01</v>
+      </c>
+      <c r="X40">
+        <v>97</v>
+      </c>
+      <c r="Y40">
+        <v>0.01</v>
+      </c>
+      <c r="Z40">
         <v>250</v>
       </c>
-      <c r="V40">
+      <c r="AA40">
         <v>350</v>
       </c>
-      <c r="W40">
+      <c r="AB40">
         <v>0.96</v>
       </c>
-      <c r="X40">
+      <c r="AC40">
         <v>0.15319270833333334</v>
       </c>
-      <c r="Y40">
+      <c r="AD40">
+        <v>306.38541666666669</v>
+      </c>
+      <c r="AE40">
         <v>8.8199999999999997E-3</v>
       </c>
-      <c r="Z40">
+      <c r="AF40">
+        <v>17.64</v>
+      </c>
+      <c r="AG40">
         <v>2</v>
       </c>
-      <c r="AA40">
+      <c r="AH40">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="AB40">
+      <c r="AI40">
+        <v>27.4</v>
+      </c>
+      <c r="AJ40">
         <v>0.1757127083333333</v>
       </c>
-    </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK40">
+        <v>351.42541666666659</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>73</v>
       </c>
       <c r="C41" t="s">
         <v>127</v>
       </c>
-      <c r="D41">
+      <c r="D41" t="s">
+        <v>140</v>
+      </c>
+      <c r="E41">
         <v>0.19434000000000001</v>
       </c>
-      <c r="E41">
+      <c r="F41">
+        <v>388.68</v>
+      </c>
+      <c r="G41">
         <v>1000</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
       <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J41">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>1.5E-3</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>1.8E-3</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>1E-3</v>
+        <v>0.3</v>
       </c>
       <c r="O41">
-        <v>1.5E-3</v>
+        <v>0.15</v>
       </c>
       <c r="P41">
-        <v>1E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q41">
-        <v>2E-3</v>
+        <v>0.18</v>
       </c>
       <c r="R41">
-        <v>2E-3</v>
+        <v>0.1</v>
       </c>
       <c r="S41">
-        <v>2.0000000000000001E-4</v>
+        <v>0.15</v>
       </c>
       <c r="T41">
-        <v>0.92</v>
+        <v>0.01</v>
       </c>
       <c r="U41">
+        <v>0.2</v>
+      </c>
+      <c r="V41">
+        <v>0.2</v>
+      </c>
+      <c r="W41">
+        <v>0.02</v>
+      </c>
+      <c r="X41">
+        <v>92</v>
+      </c>
+      <c r="Y41">
+        <v>0.02</v>
+      </c>
+      <c r="Z41">
         <v>54.9</v>
       </c>
-      <c r="V41">
+      <c r="AA41">
         <v>345</v>
       </c>
-      <c r="W41">
+      <c r="AB41">
         <v>0.85</v>
       </c>
-      <c r="X41">
+      <c r="AC41">
         <v>0.2286352941176471</v>
       </c>
-      <c r="Y41">
+      <c r="AD41">
+        <v>457.27058823529421</v>
+      </c>
+      <c r="AE41">
         <v>8.6940000000000003E-3</v>
       </c>
-      <c r="Z41">
+      <c r="AF41">
+        <v>17.388000000000002</v>
+      </c>
+      <c r="AG41">
         <v>7</v>
       </c>
-      <c r="AA41">
+      <c r="AH41">
         <v>1.67E-2</v>
       </c>
-      <c r="AB41">
+      <c r="AI41">
+        <v>33.4</v>
+      </c>
+      <c r="AJ41">
         <v>0.25402929411764708</v>
       </c>
-    </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK41">
+        <v>508.05858823529417</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -4206,14 +5206,11 @@
       <c r="C42" t="s">
         <v>74</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>0.25</v>
       </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
       <c r="F42">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4221,82 +5218,103 @@
       <c r="H42">
         <v>0</v>
       </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
       <c r="J42">
-        <v>1.95E-2</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>4.1000000000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="L42">
-        <v>9.5999999999999992E-3</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>2.3E-3</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>1.9499999999999999E-3</v>
+        <v>1.95</v>
       </c>
       <c r="O42">
-        <v>1.1000000000000001E-3</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="P42">
-        <v>2.0000000000000001E-4</v>
+        <v>0.96</v>
       </c>
       <c r="Q42">
-        <v>2.0000000000000001E-4</v>
+        <v>0.22999999999999998</v>
       </c>
       <c r="R42">
-        <v>2.6999999999999999E-5</v>
+        <v>0.19499999999999998</v>
       </c>
       <c r="S42">
-        <v>6.4999999999999997E-4</v>
+        <v>0.11</v>
       </c>
       <c r="T42">
-        <v>0.85</v>
+        <v>0.02</v>
       </c>
       <c r="U42">
+        <v>0.02</v>
+      </c>
+      <c r="V42">
+        <v>2.6999999999999997E-3</v>
+      </c>
+      <c r="W42">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="X42">
+        <v>85</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
         <v>167.38</v>
       </c>
-      <c r="V42">
+      <c r="AA42">
         <v>500</v>
       </c>
-      <c r="W42">
+      <c r="AB42">
         <v>0.75</v>
       </c>
-      <c r="X42">
+      <c r="AC42">
         <v>0.33333333333333331</v>
       </c>
-      <c r="Y42">
+      <c r="AD42">
+        <v>666.66666666666663</v>
+      </c>
+      <c r="AE42">
         <v>1.26E-2</v>
       </c>
-      <c r="Z42">
+      <c r="AF42">
+        <v>25.2</v>
+      </c>
+      <c r="AG42">
         <v>8</v>
       </c>
-      <c r="AA42">
+      <c r="AH42">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="AB42">
+      <c r="AI42">
+        <v>34.6</v>
+      </c>
+      <c r="AJ42">
         <v>0.36323333333333335</v>
       </c>
-    </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK42">
+        <v>726.4666666666667</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>75</v>
       </c>
       <c r="C43" t="s">
         <v>75</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>0.25</v>
       </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
       <c r="F43">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4304,82 +5322,103 @@
       <c r="H43">
         <v>0</v>
       </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
       <c r="J43">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>1E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O43">
-        <v>1.1999999999999999E-3</v>
+        <v>0.3</v>
       </c>
       <c r="P43">
-        <v>2.0000000000000001E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q43">
-        <v>4.0000000000000002E-4</v>
+        <v>0.2</v>
       </c>
       <c r="R43">
-        <v>2.9999999999999997E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S43">
-        <v>2.9999999999999997E-4</v>
+        <v>0.12</v>
       </c>
       <c r="T43">
-        <v>0.85</v>
+        <v>0.02</v>
       </c>
       <c r="U43">
+        <v>0.04</v>
+      </c>
+      <c r="V43">
+        <v>0.03</v>
+      </c>
+      <c r="W43">
+        <v>0.03</v>
+      </c>
+      <c r="X43">
+        <v>85</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
         <v>119.78</v>
       </c>
-      <c r="V43">
+      <c r="AA43">
         <v>415</v>
       </c>
-      <c r="W43">
+      <c r="AB43">
         <v>0.74</v>
       </c>
-      <c r="X43">
+      <c r="AC43">
         <v>0.33783783783783788</v>
       </c>
-      <c r="Y43">
+      <c r="AD43">
+        <v>675.67567567567573</v>
+      </c>
+      <c r="AE43">
         <v>1.0458E-2</v>
       </c>
-      <c r="Z43">
+      <c r="AF43">
+        <v>20.916</v>
+      </c>
+      <c r="AG43">
         <v>8</v>
       </c>
-      <c r="AA43">
+      <c r="AH43">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="AB43">
+      <c r="AI43">
+        <v>34.6</v>
+      </c>
+      <c r="AJ43">
         <v>0.36559583783783789</v>
       </c>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK43">
+        <v>731.19167567567581</v>
+      </c>
+    </row>
+    <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>76</v>
       </c>
       <c r="C44" t="s">
         <v>76</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>0.25</v>
       </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
       <c r="F44">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4387,82 +5426,103 @@
       <c r="H44">
         <v>0</v>
       </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
       <c r="J44">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L44">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M44">
-        <v>1.8E-3</v>
+        <v>0</v>
       </c>
       <c r="N44">
-        <v>1E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O44">
-        <v>1.1999999999999999E-3</v>
+        <v>0.3</v>
       </c>
       <c r="P44">
-        <v>2.0000000000000001E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q44">
-        <v>4.0000000000000002E-4</v>
+        <v>0.18</v>
       </c>
       <c r="R44">
-        <v>2.9999999999999997E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S44">
-        <v>2.9999999999999997E-4</v>
+        <v>0.12</v>
       </c>
       <c r="T44">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="U44">
+        <v>0.04</v>
+      </c>
+      <c r="V44">
+        <v>0.03</v>
+      </c>
+      <c r="W44">
+        <v>0.03</v>
+      </c>
+      <c r="X44">
+        <v>95</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
         <v>489</v>
       </c>
-      <c r="V44">
+      <c r="AA44">
         <v>387</v>
       </c>
-      <c r="W44">
+      <c r="AB44">
         <v>0.88</v>
       </c>
-      <c r="X44">
+      <c r="AC44">
         <v>0.28409090909090906</v>
       </c>
-      <c r="Y44">
+      <c r="AD44">
+        <v>568.18181818181813</v>
+      </c>
+      <c r="AE44">
         <v>9.7523999999999996E-3</v>
       </c>
-      <c r="Z44">
+      <c r="AF44">
+        <v>19.504799999999999</v>
+      </c>
+      <c r="AG44">
         <v>5</v>
       </c>
-      <c r="AA44">
+      <c r="AH44">
         <v>1.55E-2</v>
       </c>
-      <c r="AB44">
+      <c r="AI44">
+        <v>31</v>
+      </c>
+      <c r="AJ44">
         <v>0.30934330909090907</v>
       </c>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK44">
+        <v>618.68661818181818</v>
+      </c>
+    </row>
+    <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>77</v>
       </c>
       <c r="C45" t="s">
         <v>77</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>0.25</v>
       </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
       <c r="F45">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4470,82 +5530,103 @@
       <c r="H45">
         <v>0</v>
       </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
       <c r="J45">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L45">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>1E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O45">
-        <v>1.1999999999999999E-3</v>
+        <v>0.3</v>
       </c>
       <c r="P45">
-        <v>2.0000000000000001E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q45">
-        <v>4.0000000000000002E-4</v>
+        <v>0.2</v>
       </c>
       <c r="R45">
-        <v>2.9999999999999997E-4</v>
+        <v>0.1</v>
       </c>
       <c r="S45">
-        <v>2.9999999999999997E-4</v>
+        <v>0.12</v>
       </c>
       <c r="T45">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="U45">
+        <v>0.04</v>
+      </c>
+      <c r="V45">
+        <v>0.03</v>
+      </c>
+      <c r="W45">
+        <v>0.03</v>
+      </c>
+      <c r="X45">
+        <v>95</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
         <v>119.16</v>
       </c>
-      <c r="V45">
+      <c r="AA45">
         <v>350</v>
       </c>
-      <c r="W45">
+      <c r="AB45">
         <v>0.8</v>
       </c>
-      <c r="X45">
+      <c r="AC45">
         <v>0.3125</v>
       </c>
-      <c r="Y45">
+      <c r="AD45">
+        <v>625</v>
+      </c>
+      <c r="AE45">
         <v>8.8199999999999997E-3</v>
       </c>
-      <c r="Z45">
+      <c r="AF45">
+        <v>17.64</v>
+      </c>
+      <c r="AG45">
         <v>6</v>
       </c>
-      <c r="AA45">
+      <c r="AH45">
         <v>1.61E-2</v>
       </c>
-      <c r="AB45">
+      <c r="AI45">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="AJ45">
         <v>0.33742</v>
       </c>
-    </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK45">
+        <v>674.84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>78</v>
       </c>
       <c r="C46" t="s">
         <v>78</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>0.25</v>
       </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
       <c r="F46">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -4553,82 +5634,103 @@
       <c r="H46">
         <v>0</v>
       </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
       <c r="J46">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>1.5E-3</v>
+        <v>0</v>
       </c>
       <c r="L46">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>5.0000000000000001E-4</v>
+        <v>0.3</v>
       </c>
       <c r="O46">
-        <v>4.0000000000000002E-4</v>
+        <v>0.15</v>
       </c>
       <c r="P46">
-        <v>1E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q46">
-        <v>1E-4</v>
+        <v>0.2</v>
       </c>
       <c r="R46">
-        <v>1E-4</v>
+        <v>0.05</v>
       </c>
       <c r="S46">
-        <v>1E-4</v>
+        <v>0.04</v>
       </c>
       <c r="T46">
-        <v>0.98</v>
+        <v>0.01</v>
       </c>
       <c r="U46">
+        <v>0.01</v>
+      </c>
+      <c r="V46">
+        <v>0.01</v>
+      </c>
+      <c r="W46">
+        <v>0.01</v>
+      </c>
+      <c r="X46">
+        <v>98</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
         <v>119.78</v>
       </c>
-      <c r="V46">
+      <c r="AA46">
         <v>350</v>
       </c>
-      <c r="W46">
+      <c r="AB46">
         <v>0.93</v>
       </c>
-      <c r="X46">
+      <c r="AC46">
         <v>0.26881720430107525</v>
       </c>
-      <c r="Y46">
+      <c r="AD46">
+        <v>537.63440860215053</v>
+      </c>
+      <c r="AE46">
         <v>8.8199999999999997E-3</v>
       </c>
-      <c r="Z46">
+      <c r="AF46">
+        <v>17.64</v>
+      </c>
+      <c r="AG46">
         <v>3</v>
       </c>
-      <c r="AA46">
+      <c r="AH46">
         <v>1.43E-2</v>
       </c>
-      <c r="AB46">
+      <c r="AI46">
+        <v>28.6</v>
+      </c>
+      <c r="AJ46">
         <v>0.29193720430107528</v>
       </c>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK46">
+        <v>583.87440860215054</v>
+      </c>
+    </row>
+    <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>79</v>
       </c>
       <c r="C47" t="s">
         <v>79</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>0.25</v>
       </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
       <c r="F47">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -4636,82 +5738,103 @@
       <c r="H47">
         <v>0</v>
       </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
       <c r="J47">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>1.5E-3</v>
+        <v>0</v>
       </c>
       <c r="L47">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>1.8E-3</v>
+        <v>0</v>
       </c>
       <c r="N47">
-        <v>5.0000000000000001E-4</v>
+        <v>0.3</v>
       </c>
       <c r="O47">
-        <v>4.0000000000000002E-4</v>
+        <v>0.15</v>
       </c>
       <c r="P47">
-        <v>1E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q47">
-        <v>1E-4</v>
+        <v>0.18</v>
       </c>
       <c r="R47">
-        <v>1E-4</v>
+        <v>0.05</v>
       </c>
       <c r="S47">
-        <v>1E-4</v>
+        <v>0.04</v>
       </c>
       <c r="T47">
-        <v>0.97</v>
+        <v>0.01</v>
       </c>
       <c r="U47">
+        <v>0.01</v>
+      </c>
+      <c r="V47">
+        <v>0.01</v>
+      </c>
+      <c r="W47">
+        <v>0.01</v>
+      </c>
+      <c r="X47">
+        <v>97</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
         <v>250</v>
       </c>
-      <c r="V47">
+      <c r="AA47">
         <v>350</v>
       </c>
-      <c r="W47">
+      <c r="AB47">
         <v>0.96</v>
       </c>
-      <c r="X47">
+      <c r="AC47">
         <v>0.26041666666666669</v>
       </c>
-      <c r="Y47">
+      <c r="AD47">
+        <v>520.83333333333337</v>
+      </c>
+      <c r="AE47">
         <v>8.8199999999999997E-3</v>
       </c>
-      <c r="Z47">
+      <c r="AF47">
+        <v>17.64</v>
+      </c>
+      <c r="AG47">
         <v>2</v>
       </c>
-      <c r="AA47">
+      <c r="AH47">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="AB47">
+      <c r="AI47">
+        <v>27.4</v>
+      </c>
+      <c r="AJ47">
         <v>0.28293666666666667</v>
       </c>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AK47">
+        <v>565.87333333333333</v>
+      </c>
+    </row>
+    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>80</v>
       </c>
       <c r="C48" t="s">
         <v>80</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>0.25</v>
       </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
       <c r="F48">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -4719,65 +5842,89 @@
       <c r="H48">
         <v>0</v>
       </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
       <c r="J48">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>1.5E-3</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>1.8E-3</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>1E-3</v>
+        <v>0.3</v>
       </c>
       <c r="O48">
-        <v>1.5E-3</v>
+        <v>0.15</v>
       </c>
       <c r="P48">
-        <v>1E-4</v>
+        <v>0.6</v>
       </c>
       <c r="Q48">
-        <v>2E-3</v>
+        <v>0.18</v>
       </c>
       <c r="R48">
-        <v>2E-3</v>
+        <v>0.1</v>
       </c>
       <c r="S48">
-        <v>2.0000000000000001E-4</v>
+        <v>0.15</v>
       </c>
       <c r="T48">
-        <v>0.92</v>
+        <v>0.01</v>
       </c>
       <c r="U48">
+        <v>0.2</v>
+      </c>
+      <c r="V48">
+        <v>0.2</v>
+      </c>
+      <c r="W48">
+        <v>0.02</v>
+      </c>
+      <c r="X48">
+        <v>92</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
         <v>54.9</v>
       </c>
-      <c r="V48">
+      <c r="AA48">
         <v>345</v>
       </c>
-      <c r="W48">
+      <c r="AB48">
         <v>0.85</v>
       </c>
-      <c r="X48">
+      <c r="AC48">
         <v>0.29411764705882354</v>
       </c>
-      <c r="Y48">
+      <c r="AD48">
+        <v>588.23529411764707</v>
+      </c>
+      <c r="AE48">
         <v>8.6940000000000003E-3</v>
       </c>
-      <c r="Z48">
+      <c r="AF48">
+        <v>17.388000000000002</v>
+      </c>
+      <c r="AG48">
         <v>7</v>
       </c>
-      <c r="AA48">
+      <c r="AH48">
         <v>1.67E-2</v>
       </c>
-      <c r="AB48">
+      <c r="AI48">
+        <v>33.4</v>
+      </c>
+      <c r="AJ48">
         <v>0.31951164705882357</v>
+      </c>
+      <c r="AK48">
+        <v>639.02329411764708</v>
       </c>
     </row>
   </sheetData>
@@ -4787,7 +5934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -4920,6 +6067,17 @@
       </c>
       <c r="C12">
         <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
